--- a/output/daily_ratings/france_ratings_2026-03-10.xlsx
+++ b/output/daily_ratings/france_ratings_2026-03-10.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004335637619027336</v>
       </c>
       <c r="P2" t="n">
-        <v>136.5194646347941</v>
+        <v>115.9769095941135</v>
       </c>
       <c r="Q2" t="n">
         <v>-3.643590000000017</v>
@@ -588,10 +588,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S2" t="n">
-        <v>107.5251536706581</v>
+        <v>92.79322133057998</v>
       </c>
       <c r="T2" t="n">
-        <v>107.5251536706581</v>
+        <v>92.79322133057998</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004335637619027336</v>
       </c>
       <c r="P3" t="n">
-        <v>128.914929837741</v>
+        <v>108.3925938992138</v>
       </c>
       <c r="Q3" t="n">
         <v>-3.643590000000017</v>
@@ -662,10 +662,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S3" t="n">
-        <v>102.2925981659489</v>
+        <v>87.56189570113865</v>
       </c>
       <c r="T3" t="n">
-        <v>102.2925981659489</v>
+        <v>87.56189570113865</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004335637619027336</v>
       </c>
       <c r="P4" t="n">
-        <v>126.6335693986251</v>
+        <v>106.1172991907439</v>
       </c>
       <c r="Q4" t="n">
         <v>-3.643590000000017</v>
@@ -736,10 +736,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S4" t="n">
-        <v>100.7228315145361</v>
+        <v>85.99249801230626</v>
       </c>
       <c r="T4" t="n">
-        <v>100.7228315145361</v>
+        <v>85.99249801230626</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004335637619027336</v>
       </c>
       <c r="P5" t="n">
-        <v>125.1126624392145</v>
+        <v>104.600436051764</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.3366600000000091</v>
@@ -810,10 +810,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S5" t="n">
-        <v>101.9517646369403</v>
+        <v>87.22720698608556</v>
       </c>
       <c r="T5" t="n">
-        <v>101.9517646369403</v>
+        <v>87.22720698608556</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004335637619027336</v>
       </c>
       <c r="P6" t="n">
-        <v>124.9605717432734</v>
+        <v>104.448749737866</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S6" t="n">
-        <v>99.5716693035001</v>
+        <v>84.84160637382915</v>
       </c>
       <c r="T6" t="n">
-        <v>99.5716693035001</v>
+        <v>84.84160637382915</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>6.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004335637619027336</v>
       </c>
       <c r="P7" t="n">
-        <v>115.8351299868097</v>
+        <v>95.34757090398641</v>
       </c>
       <c r="Q7" t="n">
         <v>-3.643590000000017</v>
@@ -958,10 +958,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S7" t="n">
-        <v>93.29260269784899</v>
+        <v>78.56401561849957</v>
       </c>
       <c r="T7" t="n">
-        <v>93.29260269784899</v>
+        <v>78.56401561849957</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>12.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004335637619027336</v>
       </c>
       <c r="P8" t="n">
-        <v>97.5842464738823</v>
+        <v>77.14521323622725</v>
       </c>
       <c r="Q8" t="n">
         <v>-3.643590000000017</v>
@@ -1032,10 +1032,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S8" t="n">
-        <v>80.73446948654677</v>
+        <v>66.00883410784036</v>
       </c>
       <c r="T8" t="n">
-        <v>80.73446948654677</v>
+        <v>66.00883410784036</v>
       </c>
     </row>
     <row r="9">
@@ -1096,10 +1096,10 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P9" t="n">
-        <v>103.5451411533356</v>
+        <v>102.3196309845391</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.438970000000012</v>
@@ -1108,10 +1108,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S9" t="n">
-        <v>86.96520315241057</v>
+        <v>85.9574818303136</v>
       </c>
       <c r="T9" t="n">
-        <v>86.96520315241057</v>
+        <v>85.9574818303136</v>
       </c>
     </row>
     <row r="10">
@@ -1170,10 +1170,10 @@
         <v>0.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P10" t="n">
-        <v>103.1670326682879</v>
+        <v>101.9427030419156</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.438970000000012</v>
@@ -1182,10 +1182,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S10" t="n">
-        <v>86.70503291351832</v>
+        <v>85.69749360118111</v>
       </c>
       <c r="T10" t="n">
-        <v>86.70503291351832</v>
+        <v>85.69749360118111</v>
       </c>
     </row>
     <row r="11">
@@ -1244,10 +1244,10 @@
         <v>0.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P11" t="n">
-        <v>103.0409965066054</v>
+        <v>101.8170603943745</v>
       </c>
       <c r="Q11" t="n">
         <v>-5.848210000000009</v>
@@ -1256,10 +1256,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S11" t="n">
-        <v>83.58438386942623</v>
+        <v>82.56953205858018</v>
       </c>
       <c r="T11" t="n">
-        <v>83.58438386942623</v>
+        <v>82.56953205858018</v>
       </c>
     </row>
     <row r="12">
@@ -1318,10 +1318,10 @@
         <v>1.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P12" t="n">
-        <v>99.89009246454111</v>
+        <v>98.6759942058458</v>
       </c>
       <c r="Q12" t="n">
         <v>1.867959999999982</v>
@@ -1330,10 +1330,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S12" t="n">
-        <v>86.72566839979822</v>
+        <v>85.72523638170055</v>
       </c>
       <c r="T12" t="n">
-        <v>86.72566839979822</v>
+        <v>85.72523638170055</v>
       </c>
     </row>
     <row r="13">
@@ -1392,10 +1392,10 @@
         <v>4.45</v>
       </c>
       <c r="O13" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P13" t="n">
-        <v>92.32792276358695</v>
+        <v>91.13743535337693</v>
       </c>
       <c r="Q13" t="n">
         <v>-5.848210000000009</v>
@@ -1404,10 +1404,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S13" t="n">
-        <v>76.21289376747939</v>
+        <v>75.20319889982669</v>
       </c>
       <c r="T13" t="n">
-        <v>76.21289376747939</v>
+        <v>75.20319889982669</v>
       </c>
     </row>
     <row r="14">
@@ -1466,10 +1466,10 @@
         <v>4.600000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P14" t="n">
-        <v>91.94981427853924</v>
+        <v>90.76050741075349</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.438970000000012</v>
@@ -1478,10 +1478,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S14" t="n">
-        <v>78.98664915971514</v>
+        <v>77.98450947025098</v>
       </c>
       <c r="T14" t="n">
-        <v>78.98664915971514</v>
+        <v>77.98450947025098</v>
       </c>
     </row>
     <row r="15">
@@ -1540,10 +1540,10 @@
         <v>5.350000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P15" t="n">
-        <v>90.0592718533007</v>
+        <v>88.87586769763627</v>
       </c>
       <c r="Q15" t="n">
         <v>-5.848210000000009</v>
@@ -1552,10 +1552,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S15" t="n">
-        <v>74.65187233412594</v>
+        <v>73.64326952503181</v>
       </c>
       <c r="T15" t="n">
-        <v>74.65187233412594</v>
+        <v>73.64326952503181</v>
       </c>
     </row>
     <row r="16">
@@ -1614,10 +1614,10 @@
         <v>5.850000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P16" t="n">
-        <v>88.798910236475</v>
+        <v>87.61944122222479</v>
       </c>
       <c r="Q16" t="n">
         <v>-5.848210000000009</v>
@@ -1626,10 +1626,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S16" t="n">
-        <v>73.78463820448513</v>
+        <v>72.77664209459023</v>
       </c>
       <c r="T16" t="n">
-        <v>73.78463820448513</v>
+        <v>72.77664209459023</v>
       </c>
     </row>
     <row r="17">
@@ -1688,10 +1688,10 @@
         <v>6.600000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P17" t="n">
-        <v>86.90836781123646</v>
+        <v>85.73480150910757</v>
       </c>
       <c r="Q17" t="n">
         <v>-5.848210000000009</v>
@@ -1700,10 +1700,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S17" t="n">
-        <v>72.48378701002392</v>
+        <v>71.47670094892784</v>
       </c>
       <c r="T17" t="n">
-        <v>72.48378701002392</v>
+        <v>71.47670094892784</v>
       </c>
     </row>
     <row r="18">
@@ -1762,10 +1762,10 @@
         <v>10.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P18" t="n">
-        <v>76.82547487663089</v>
+        <v>75.68338970581576</v>
       </c>
       <c r="Q18" t="n">
         <v>1.867959999999982</v>
@@ -1774,10 +1774,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S18" t="n">
-        <v>70.85528382737149</v>
+        <v>69.86595440461947</v>
       </c>
       <c r="T18" t="n">
-        <v>70.85528382737149</v>
+        <v>69.86595440461947</v>
       </c>
     </row>
     <row r="19">
@@ -1836,10 +1836,10 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P19" t="n">
-        <v>68.00294355885103</v>
+        <v>66.88840437793542</v>
       </c>
       <c r="Q19" t="n">
         <v>-5.848210000000009</v>
@@ -1848,10 +1848,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S19" t="n">
-        <v>59.47527506541185</v>
+        <v>58.47728949230401</v>
       </c>
       <c r="T19" t="n">
-        <v>59.47527506541185</v>
+        <v>58.47728949230401</v>
       </c>
     </row>
     <row r="20">
@@ -1910,10 +1910,10 @@
         <v>14.13</v>
       </c>
       <c r="O20" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P20" t="n">
-        <v>67.92732186184149</v>
+        <v>66.81301878941073</v>
       </c>
       <c r="Q20" t="n">
         <v>-5.848210000000009</v>
@@ -1922,10 +1922,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S20" t="n">
-        <v>59.4232410176334</v>
+        <v>58.42529184647752</v>
       </c>
       <c r="T20" t="n">
-        <v>59.4232410176334</v>
+        <v>58.42529184647752</v>
       </c>
     </row>
     <row r="21">
@@ -1984,10 +1984,10 @@
         <v>24.13</v>
       </c>
       <c r="O21" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.00508150372799078</v>
       </c>
       <c r="P21" t="n">
-        <v>47.97405823276252</v>
+        <v>46.92460691118058</v>
       </c>
       <c r="Q21" t="n">
         <v>2.970269999999999</v>
@@ -2056,10 +2056,10 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P22" t="n">
-        <v>94.79969824058446</v>
+        <v>97.31177061680468</v>
       </c>
       <c r="Q22" t="n">
         <v>1.867959999999982</v>
@@ -2068,10 +2068,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S22" t="n">
-        <v>81.75975906833247</v>
+        <v>83.3969919483918</v>
       </c>
       <c r="T22" t="n">
-        <v>81.75975906833247</v>
+        <v>83.3969919483918</v>
       </c>
     </row>
     <row r="23">
@@ -2130,10 +2130,10 @@
         <v>1.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P23" t="n">
-        <v>91.48166144769434</v>
+        <v>94.00414699969417</v>
       </c>
       <c r="Q23" t="n">
         <v>1.867959999999982</v>
@@ -2142,10 +2142,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S23" t="n">
-        <v>79.47667244320542</v>
+        <v>81.11553942230934</v>
       </c>
       <c r="T23" t="n">
-        <v>79.47667244320542</v>
+        <v>81.11553942230934</v>
       </c>
     </row>
     <row r="24">
@@ -2204,10 +2204,10 @@
         <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P24" t="n">
-        <v>87.68961939867704</v>
+        <v>90.22400572299645</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S24" t="n">
-        <v>76.86743058591738</v>
+        <v>78.50816510678654</v>
       </c>
       <c r="T24" t="n">
-        <v>76.86743058591738</v>
+        <v>78.50816510678654</v>
       </c>
     </row>
     <row r="25">
@@ -2278,10 +2278,10 @@
         <v>8.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P25" t="n">
-        <v>79.15752478838813</v>
+        <v>81.71868785042658</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S25" t="n">
-        <v>70.99663640701925</v>
+        <v>72.64157289686021</v>
       </c>
       <c r="T25" t="n">
-        <v>70.99663640701925</v>
+        <v>72.64157289686021</v>
       </c>
     </row>
     <row r="26">
@@ -2352,10 +2352,10 @@
         <v>9.75</v>
       </c>
       <c r="O26" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P26" t="n">
-        <v>76.31349325162516</v>
+        <v>78.88358189290329</v>
       </c>
       <c r="Q26" t="n">
         <v>-2.541280000000015</v>
@@ -2364,10 +2364,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S26" t="n">
-        <v>66.00577938292521</v>
+        <v>67.64474336066134</v>
       </c>
       <c r="T26" t="n">
-        <v>66.00577938292521</v>
+        <v>67.64474336066134</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2426,10 @@
         <v>10</v>
       </c>
       <c r="O27" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P27" t="n">
-        <v>75.839487995498</v>
+        <v>78.41106423331607</v>
       </c>
       <c r="Q27" t="n">
         <v>1.867959999999982</v>
@@ -2438,10 +2438,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S27" t="n">
-        <v>68.71354978189223</v>
+        <v>70.36012037077775</v>
       </c>
       <c r="T27" t="n">
-        <v>68.71354978189223</v>
+        <v>70.36012037077775</v>
       </c>
     </row>
     <row r="28">
@@ -2500,10 +2500,10 @@
         <v>14</v>
       </c>
       <c r="O28" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P28" t="n">
-        <v>68.25540389746342</v>
+        <v>70.85078167992063</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S28" t="n">
-        <v>63.49506606731612</v>
+        <v>65.14537173973216</v>
       </c>
       <c r="T28" t="n">
-        <v>63.49506606731612</v>
+        <v>65.14537173973216</v>
       </c>
     </row>
     <row r="29">
@@ -2574,10 +2574,10 @@
         <v>19</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P29" t="n">
-        <v>58.77529877492019</v>
+        <v>61.40042848817633</v>
       </c>
       <c r="Q29" t="n">
         <v>1.867959999999982</v>
@@ -2586,10 +2586,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S29" t="n">
-        <v>56.971961424096</v>
+        <v>58.62693595092513</v>
       </c>
       <c r="T29" t="n">
-        <v>56.971961424096</v>
+        <v>58.62693595092513</v>
       </c>
     </row>
     <row r="30">
@@ -2650,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P30" t="n">
-        <v>79.49946547952493</v>
+        <v>82.02982681329215</v>
       </c>
       <c r="Q30" t="n">
         <v>1.867959999999982</v>
@@ -2662,10 +2662,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S30" t="n">
-        <v>71.23192018090447</v>
+        <v>72.85618279658406</v>
       </c>
       <c r="T30" t="n">
-        <v>71.23192018090447</v>
+        <v>72.85618279658406</v>
       </c>
     </row>
     <row r="31">
@@ -2724,10 +2724,10 @@
         <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P31" t="n">
-        <v>66.38541186811374</v>
+        <v>68.95692975135975</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2736,10 +2736,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S31" t="n">
-        <v>62.20835526276725</v>
+        <v>63.83907641517044</v>
       </c>
       <c r="T31" t="n">
-        <v>62.20835526276725</v>
+        <v>63.83907641517044</v>
       </c>
     </row>
     <row r="32">
@@ -2798,10 +2798,10 @@
         <v>7.75</v>
       </c>
       <c r="O32" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P32" t="n">
-        <v>64.98033469546253</v>
+        <v>67.55626220900984</v>
       </c>
       <c r="Q32" t="n">
         <v>1.867959999999982</v>
@@ -2810,10 +2810,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S32" t="n">
-        <v>61.24154473582397</v>
+        <v>62.87295787430469</v>
       </c>
       <c r="T32" t="n">
-        <v>61.24154473582397</v>
+        <v>62.87295787430469</v>
       </c>
     </row>
     <row r="33">
@@ -2872,10 +2872,10 @@
         <v>7.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P33" t="n">
-        <v>64.88666288395245</v>
+        <v>67.4628843728532</v>
       </c>
       <c r="Q33" t="n">
         <v>-2.541280000000015</v>
@@ -2884,10 +2884,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S33" t="n">
-        <v>58.14316506956641</v>
+        <v>59.76725117202354</v>
       </c>
       <c r="T33" t="n">
-        <v>58.14316506956641</v>
+        <v>59.76725117202354</v>
       </c>
     </row>
     <row r="34">
@@ -2946,10 +2946,10 @@
         <v>9.050000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P34" t="n">
-        <v>62.54486759620045</v>
+        <v>65.12843846893669</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S34" t="n">
-        <v>56.53181419132762</v>
+        <v>58.15705360391396</v>
       </c>
       <c r="T34" t="n">
-        <v>56.53181419132762</v>
+        <v>58.15705360391396</v>
       </c>
     </row>
     <row r="35">
@@ -3020,10 +3020,10 @@
         <v>10.3</v>
       </c>
       <c r="O35" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P35" t="n">
-        <v>60.20307230844845</v>
+        <v>62.79399256502019</v>
       </c>
       <c r="Q35" t="n">
         <v>1.867959999999982</v>
@@ -3032,10 +3032,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S35" t="n">
-        <v>57.95438894421684</v>
+        <v>59.58815483536115</v>
       </c>
       <c r="T35" t="n">
-        <v>57.95438894421684</v>
+        <v>59.58815483536115</v>
       </c>
     </row>
     <row r="36">
@@ -3094,10 +3094,10 @@
         <v>12.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P36" t="n">
-        <v>55.51948173294446</v>
+        <v>58.12510075718719</v>
       </c>
       <c r="Q36" t="n">
         <v>1.867959999999982</v>
@@ -3106,10 +3106,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S36" t="n">
-        <v>54.73168718773927</v>
+        <v>56.36775969914199</v>
       </c>
       <c r="T36" t="n">
-        <v>54.73168718773927</v>
+        <v>56.36775969914199</v>
       </c>
     </row>
     <row r="37">
@@ -3168,10 +3168,10 @@
         <v>14.55</v>
       </c>
       <c r="O37" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P37" t="n">
-        <v>52.24096833009166</v>
+        <v>54.85687649170409</v>
       </c>
       <c r="Q37" t="n">
         <v>1.867959999999982</v>
@@ -3180,10 +3180,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S37" t="n">
-        <v>52.47579595820496</v>
+        <v>54.11348310378858</v>
       </c>
       <c r="T37" t="n">
-        <v>52.47579595820496</v>
+        <v>54.11348310378858</v>
       </c>
     </row>
     <row r="38">
@@ -3242,10 +3242,10 @@
         <v>16.55</v>
       </c>
       <c r="O38" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P38" t="n">
-        <v>48.49409586968846</v>
+        <v>51.12176304543769</v>
       </c>
       <c r="Q38" t="n">
         <v>1.867959999999982</v>
@@ -3254,10 +3254,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S38" t="n">
-        <v>49.8976345530229</v>
+        <v>51.53716699481325</v>
       </c>
       <c r="T38" t="n">
-        <v>49.8976345530229</v>
+        <v>51.53716699481325</v>
       </c>
     </row>
     <row r="39">
@@ -3316,10 +3316,10 @@
         <v>18.55</v>
       </c>
       <c r="O39" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.005213376090369017</v>
       </c>
       <c r="P39" t="n">
-        <v>44.74722340928526</v>
+        <v>47.38664959917129</v>
       </c>
       <c r="Q39" t="n">
         <v>1.867959999999982</v>
@@ -3328,10 +3328,10 @@
         <v>2.832736816988787</v>
       </c>
       <c r="S39" t="n">
-        <v>47.31947314784084</v>
+        <v>48.96085088583794</v>
       </c>
       <c r="T39" t="n">
-        <v>47.31947314784084</v>
+        <v>48.96085088583794</v>
       </c>
     </row>
     <row r="40">
@@ -3392,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P40" t="n">
-        <v>112.7020973039985</v>
+        <v>107.5963851265308</v>
       </c>
       <c r="Q40" t="n">
         <v>-2.541280000000015</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>89.09502054016818</v>
+        <v>85.24385814029867</v>
       </c>
       <c r="T40" t="n">
-        <v>89.09502054016818</v>
+        <v>85.24385814029867</v>
       </c>
     </row>
     <row r="41">
@@ -3466,10 +3466,10 @@
         <v>0.1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P41" t="n">
-        <v>112.5098526142958</v>
+        <v>107.4047437688197</v>
       </c>
       <c r="Q41" t="n">
         <v>4.072579999999988</v>
@@ -3478,10 +3478,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>93.51362857310696</v>
+        <v>89.67362060441593</v>
       </c>
       <c r="T41" t="n">
-        <v>93.51362857310696</v>
+        <v>89.67362060441593</v>
       </c>
     </row>
     <row r="42">
@@ -3540,10 +3540,10 @@
         <v>2.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P42" t="n">
-        <v>107.7037353717274</v>
+        <v>102.6137098260423</v>
       </c>
       <c r="Q42" t="n">
         <v>-2.541280000000015</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>85.65572978258371</v>
+        <v>81.80702902463318</v>
       </c>
       <c r="T42" t="n">
-        <v>85.65572978258371</v>
+        <v>81.80702902463318</v>
       </c>
     </row>
     <row r="43">
@@ -3614,10 +3614,10 @@
         <v>7.6</v>
       </c>
       <c r="O43" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P43" t="n">
-        <v>98.09150088659084</v>
+        <v>93.03164194048746</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>79.04170909492132</v>
+        <v>75.19774226373799</v>
       </c>
       <c r="T43" t="n">
-        <v>79.04170909492132</v>
+        <v>75.19774226373799</v>
       </c>
     </row>
     <row r="44">
@@ -3688,10 +3688,10 @@
         <v>9.1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P44" t="n">
-        <v>95.20783054104984</v>
+        <v>90.157021574821</v>
       </c>
       <c r="Q44" t="n">
         <v>2.970269999999999</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>80.84990992753262</v>
+        <v>77.01657973491541</v>
       </c>
       <c r="T44" t="n">
-        <v>80.84990992753262</v>
+        <v>77.01657973491541</v>
       </c>
     </row>
     <row r="45">
@@ -3762,10 +3762,10 @@
         <v>9.15</v>
       </c>
       <c r="O45" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P45" t="n">
-        <v>95.11170819619848</v>
+        <v>90.06120089596546</v>
       </c>
       <c r="Q45" t="n">
         <v>5.174889999999976</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>82.30073253621998</v>
+        <v>78.47113626708483</v>
       </c>
       <c r="T45" t="n">
-        <v>82.30073253621998</v>
+        <v>78.47113626708483</v>
       </c>
     </row>
     <row r="46">
@@ -3836,10 +3836,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P46" t="n">
-        <v>94.82334116164438</v>
+        <v>89.7737388593988</v>
       </c>
       <c r="Q46" t="n">
         <v>0.7656499999999937</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>79.06838628446212</v>
+        <v>75.23155886470121</v>
       </c>
       <c r="T46" t="n">
-        <v>79.06838628446212</v>
+        <v>75.23155886470121</v>
       </c>
     </row>
     <row r="47">
@@ -3910,10 +3910,10 @@
         <v>9.4</v>
       </c>
       <c r="O47" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P47" t="n">
-        <v>94.63109647194165</v>
+        <v>89.58209750168771</v>
       </c>
       <c r="Q47" t="n">
         <v>-1.438970000000012</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>77.41914305514484</v>
+        <v>73.57872372970492</v>
       </c>
       <c r="T47" t="n">
-        <v>77.41914305514484</v>
+        <v>73.57872372970492</v>
       </c>
     </row>
     <row r="48">
@@ -3984,10 +3984,10 @@
         <v>9.450000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P48" t="n">
-        <v>94.53497412709028</v>
+        <v>89.48627682283217</v>
       </c>
       <c r="Q48" t="n">
         <v>-1.438970000000012</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>77.35300284826823</v>
+        <v>73.51263086209596</v>
       </c>
       <c r="T48" t="n">
-        <v>77.35300284826823</v>
+        <v>73.51263086209596</v>
       </c>
     </row>
     <row r="49">
@@ -4058,10 +4058,10 @@
         <v>10.45</v>
       </c>
       <c r="O49" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P49" t="n">
-        <v>92.61252723006295</v>
+        <v>87.56986324572119</v>
       </c>
       <c r="Q49" t="n">
         <v>-1.438970000000012</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>76.03019871073573</v>
+        <v>72.19077350991694</v>
       </c>
       <c r="T49" t="n">
-        <v>76.03019871073573</v>
+        <v>72.19077350991694</v>
       </c>
     </row>
     <row r="50">
@@ -4132,10 +4132,10 @@
         <v>11.2</v>
       </c>
       <c r="O50" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P50" t="n">
-        <v>91.17069205729246</v>
+        <v>86.13255306288796</v>
       </c>
       <c r="Q50" t="n">
         <v>2.970269999999999</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>78.0720212387144</v>
+        <v>74.24067929533943</v>
       </c>
       <c r="T50" t="n">
-        <v>78.0720212387144</v>
+        <v>74.24067929533943</v>
       </c>
     </row>
     <row r="51">
@@ -4206,10 +4206,10 @@
         <v>28.2</v>
       </c>
       <c r="O51" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P51" t="n">
-        <v>66.40824958426268</v>
+        <v>61.4475833790971</v>
       </c>
       <c r="Q51" t="n">
         <v>11.78874999999999</v>
@@ -4276,10 +4276,10 @@
         <v>30.2</v>
       </c>
       <c r="O52" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P52" t="n">
-        <v>64.48580268723535</v>
+        <v>59.53116980198613</v>
       </c>
       <c r="Q52" t="n">
         <v>-2.541280000000015</v>
@@ -4346,10 +4346,10 @@
         <v>30.95</v>
       </c>
       <c r="O53" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P53" t="n">
-        <v>63.76488510085011</v>
+        <v>58.81251471056952</v>
       </c>
       <c r="Q53" t="n">
         <v>0.7656499999999937</v>
@@ -4416,10 +4416,10 @@
         <v>31.95</v>
       </c>
       <c r="O54" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P54" t="n">
-        <v>62.80366165233645</v>
+        <v>57.85430792201403</v>
       </c>
       <c r="Q54" t="n">
         <v>-1.438970000000012</v>
@@ -4486,10 +4486,10 @@
         <v>32</v>
       </c>
       <c r="O55" t="n">
-        <v>0.004827506377435743</v>
+        <v>0.004796128218326343</v>
       </c>
       <c r="P55" t="n">
-        <v>62.75560047991077</v>
+        <v>57.80639758258626</v>
       </c>
       <c r="Q55" t="n">
         <v>4.072579999999988</v>
@@ -4558,10 +4558,10 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P56" t="n">
-        <v>132.8039766024019</v>
+        <v>115.5433463421346</v>
       </c>
       <c r="Q56" t="n">
         <v>-5.848210000000009</v>
@@ -4570,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>98.90047846826053</v>
+        <v>86.39474943812571</v>
       </c>
       <c r="T56" t="n">
-        <v>98.90047846826053</v>
+        <v>86.39474943812571</v>
       </c>
     </row>
     <row r="57">
@@ -4632,10 +4632,10 @@
         <v>0.75</v>
       </c>
       <c r="O57" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P57" t="n">
-        <v>131.3455980404564</v>
+        <v>114.0895802417527</v>
       </c>
       <c r="Q57" t="n">
         <v>-1.438970000000012</v>
@@ -4644,10 +4644,10 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>100.9309177618396</v>
+        <v>88.43330465921365</v>
       </c>
       <c r="T57" t="n">
-        <v>100.9309177618396</v>
+        <v>88.43330465921365</v>
       </c>
     </row>
     <row r="58">
@@ -4706,10 +4706,10 @@
         <v>1.5</v>
       </c>
       <c r="O58" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P58" t="n">
-        <v>129.8872194785109</v>
+        <v>112.6358141413707</v>
       </c>
       <c r="Q58" t="n">
         <v>0.7656499999999937</v>
@@ -4718,10 +4718,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>101.4443942398547</v>
+        <v>88.95121048052319</v>
       </c>
       <c r="T58" t="n">
-        <v>101.4443942398547</v>
+        <v>88.95121048052319</v>
       </c>
     </row>
     <row r="59">
@@ -4780,10 +4780,10 @@
         <v>1.75</v>
       </c>
       <c r="O59" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P59" t="n">
-        <v>129.4010932911957</v>
+        <v>112.1512254412434</v>
       </c>
       <c r="Q59" t="n">
         <v>5.174889999999976</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>104.1438244251331</v>
+        <v>91.65826142059034</v>
       </c>
       <c r="T59" t="n">
-        <v>104.1438244251331</v>
+        <v>91.65826142059034</v>
       </c>
     </row>
     <row r="60">
@@ -4854,10 +4854,10 @@
         <v>2.25</v>
       </c>
       <c r="O60" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P60" t="n">
-        <v>128.4288409165653</v>
+        <v>111.1820480409887</v>
       </c>
       <c r="Q60" t="n">
         <v>-1.438970000000012</v>
@@ -4866,10 +4866,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>98.92394508674181</v>
+        <v>86.42781750227594</v>
       </c>
       <c r="T60" t="n">
-        <v>98.92394508674181</v>
+        <v>86.42781750227594</v>
       </c>
     </row>
     <row r="61">
@@ -4928,10 +4928,10 @@
         <v>3</v>
       </c>
       <c r="O61" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P61" t="n">
-        <v>126.9704623546198</v>
+        <v>109.7282819406068</v>
       </c>
       <c r="Q61" t="n">
         <v>-5.848210000000009</v>
@@ -4940,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>94.88653311806488</v>
+        <v>82.38377512425033</v>
       </c>
       <c r="T61" t="n">
-        <v>94.88653311806488</v>
+        <v>82.38377512425033</v>
       </c>
     </row>
     <row r="62">
@@ -5002,10 +5002,10 @@
         <v>3.1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P62" t="n">
-        <v>126.7760118796937</v>
+        <v>109.5344464605558</v>
       </c>
       <c r="Q62" t="n">
         <v>6.277199999999993</v>
@@ -5014,10 +5014,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>103.0960304253271</v>
+        <v>90.61364767923563</v>
       </c>
       <c r="T62" t="n">
-        <v>103.0960304253271</v>
+        <v>90.61364767923563</v>
       </c>
     </row>
     <row r="63">
@@ -5076,10 +5076,10 @@
         <v>7.6</v>
       </c>
       <c r="O63" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P63" t="n">
-        <v>118.0257405080206</v>
+        <v>100.8118498582641</v>
       </c>
       <c r="Q63" t="n">
         <v>0.7656499999999937</v>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>93.28270536112359</v>
+        <v>80.79556270897653</v>
       </c>
       <c r="T63" t="n">
-        <v>93.28270536112359</v>
+        <v>80.79556270897653</v>
       </c>
     </row>
     <row r="64">
@@ -5150,10 +5150,10 @@
         <v>9.35</v>
       </c>
       <c r="O64" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P64" t="n">
-        <v>114.6228571968143</v>
+        <v>97.41972895737283</v>
       </c>
       <c r="Q64" t="n">
         <v>-5.848210000000009</v>
@@ -5162,10 +5162,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>86.39034879348412</v>
+        <v>73.89387949321407</v>
       </c>
       <c r="T64" t="n">
-        <v>86.39034879348412</v>
+        <v>73.89387949321407</v>
       </c>
     </row>
     <row r="65">
@@ -5224,10 +5224,10 @@
         <v>9.85</v>
       </c>
       <c r="O65" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P65" t="n">
-        <v>113.650604822184</v>
+        <v>96.45055155711819</v>
       </c>
       <c r="Q65" t="n">
         <v>6.277199999999993</v>
@@ -5236,10 +5236,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>94.06465338738687</v>
+        <v>81.58895547301596</v>
       </c>
       <c r="T65" t="n">
-        <v>94.06465338738687</v>
+        <v>81.58895547301596</v>
       </c>
     </row>
     <row r="66">
@@ -5298,10 +5298,10 @@
         <v>10</v>
       </c>
       <c r="O66" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P66" t="n">
-        <v>113.3589291097949</v>
+        <v>96.15979833704179</v>
       </c>
       <c r="Q66" t="n">
         <v>1.867959999999982</v>
@@ -5310,10 +5310,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>90.83003048874909</v>
+        <v>78.3471079577654</v>
       </c>
       <c r="T66" t="n">
-        <v>90.83003048874909</v>
+        <v>78.3471079577654</v>
       </c>
     </row>
     <row r="67">
@@ -5372,10 +5372,10 @@
         <v>11.75</v>
       </c>
       <c r="O67" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P67" t="n">
-        <v>109.9560457985886</v>
+        <v>92.76767743615055</v>
       </c>
       <c r="Q67" t="n">
         <v>-5.848210000000009</v>
@@ -5384,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>83.17919251332759</v>
+        <v>70.68510004211375</v>
       </c>
       <c r="T67" t="n">
-        <v>83.17919251332759</v>
+        <v>70.68510004211375</v>
       </c>
     </row>
     <row r="68">
@@ -5446,10 +5446,10 @@
         <v>12.75</v>
       </c>
       <c r="O68" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P68" t="n">
-        <v>108.0115410493279</v>
+        <v>90.82932263564126</v>
       </c>
       <c r="Q68" t="n">
         <v>-5.848210000000009</v>
@@ -5458,10 +5458,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>81.84121072992906</v>
+        <v>69.34810860415529</v>
       </c>
       <c r="T68" t="n">
-        <v>81.84121072992906</v>
+        <v>69.34810860415529</v>
       </c>
     </row>
     <row r="69">
@@ -5520,10 +5520,10 @@
         <v>14.25</v>
       </c>
       <c r="O69" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P69" t="n">
-        <v>105.0947839254369</v>
+        <v>87.92179043487734</v>
       </c>
       <c r="Q69" t="n">
         <v>-3.643590000000017</v>
@@ -5532,10 +5532,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>81.35120087039525</v>
+        <v>68.86327084699596</v>
       </c>
       <c r="T69" t="n">
-        <v>81.35120087039525</v>
+        <v>68.86327084699596</v>
       </c>
     </row>
     <row r="70">
@@ -5594,10 +5594,10 @@
         <v>17.25</v>
       </c>
       <c r="O70" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P70" t="n">
-        <v>99.26126967765475</v>
+        <v>82.1067260333495</v>
       </c>
       <c r="Q70" t="n">
         <v>5.174889999999976</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>83.40510678245562</v>
+        <v>70.93489413223411</v>
       </c>
       <c r="T70" t="n">
-        <v>83.40510678245562</v>
+        <v>70.93489413223411</v>
       </c>
     </row>
     <row r="71">
@@ -5668,10 +5668,10 @@
         <v>19.75</v>
       </c>
       <c r="O71" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001399966671874786</v>
       </c>
       <c r="P71" t="n">
-        <v>94.40000780450299</v>
+        <v>77.26083903207629</v>
       </c>
       <c r="Q71" t="n">
         <v>-5.848210000000009</v>
@@ -5680,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>72.47533824613924</v>
+        <v>59.98916853844603</v>
       </c>
       <c r="T71" t="n">
-        <v>72.47533824613924</v>
+        <v>59.98916853844603</v>
       </c>
     </row>
     <row r="72">
@@ -5744,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P72" t="n">
-        <v>88.12917686568329</v>
+        <v>88.32808227947145</v>
       </c>
       <c r="Q72" t="n">
         <v>1.867959999999982</v>
@@ -5756,10 +5756,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>73.46985231735908</v>
+        <v>73.4290763662826</v>
       </c>
       <c r="T72" t="n">
-        <v>73.46985231735908</v>
+        <v>73.4290763662826</v>
       </c>
     </row>
     <row r="73">
@@ -5818,10 +5818,10 @@
         <v>5</v>
       </c>
       <c r="O73" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P73" t="n">
-        <v>76.4925251285195</v>
+        <v>76.72162663519025</v>
       </c>
       <c r="Q73" t="n">
         <v>0.7656499999999937</v>
@@ -5830,10 +5830,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>64.70438195776418</v>
+        <v>64.66313173686784</v>
       </c>
       <c r="T73" t="n">
-        <v>64.70438195776418</v>
+        <v>64.66313173686784</v>
       </c>
     </row>
     <row r="74">
@@ -5892,10 +5892,10 @@
         <v>6.25</v>
       </c>
       <c r="O74" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P74" t="n">
-        <v>73.58336219422856</v>
+        <v>73.82001272411995</v>
       </c>
       <c r="Q74" t="n">
         <v>-5.848210000000009</v>
@@ -5904,10 +5904,10 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>58.15174627311892</v>
+        <v>58.09977855515128</v>
       </c>
       <c r="T74" t="n">
-        <v>58.15174627311892</v>
+        <v>58.09977855515128</v>
       </c>
     </row>
     <row r="75">
@@ -5966,10 +5966,10 @@
         <v>7.5</v>
       </c>
       <c r="O75" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P75" t="n">
-        <v>70.67419925993759</v>
+        <v>70.91839881304965</v>
       </c>
       <c r="Q75" t="n">
         <v>8.481819999999999</v>
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>66.01025733633173</v>
+        <v>65.98259467132941</v>
       </c>
       <c r="T75" t="n">
-        <v>66.01025733633173</v>
+        <v>65.98259467132941</v>
       </c>
     </row>
     <row r="76">
@@ -6040,10 +6040,10 @@
         <v>10</v>
       </c>
       <c r="O76" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P76" t="n">
-        <v>64.8558733913557</v>
+        <v>65.11517099090905</v>
       </c>
       <c r="Q76" t="n">
         <v>4.072579999999988</v>
@@ -6052,10 +6052,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>58.97283722929726</v>
+        <v>58.93848590700984</v>
       </c>
       <c r="T76" t="n">
-        <v>58.97283722929726</v>
+        <v>58.93848590700984</v>
       </c>
     </row>
     <row r="77">
@@ -6114,10 +6114,10 @@
         <v>11.5</v>
       </c>
       <c r="O77" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P77" t="n">
-        <v>61.36487787020656</v>
+        <v>61.63323429762468</v>
       </c>
       <c r="Q77" t="n">
         <v>0.7656499999999937</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>54.29529632040737</v>
+        <v>54.25582582848459</v>
       </c>
       <c r="T77" t="n">
-        <v>54.29529632040737</v>
+        <v>54.25582582848459</v>
       </c>
     </row>
     <row r="78">
@@ -6188,10 +6188,10 @@
         <v>11.6</v>
       </c>
       <c r="O78" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P78" t="n">
-        <v>61.13214483546329</v>
+        <v>61.40110518473907</v>
       </c>
       <c r="Q78" t="n">
         <v>1.867959999999982</v>
@@ -6200,10 +6200,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>54.89363794915312</v>
+        <v>54.85603812978326</v>
       </c>
       <c r="T78" t="n">
-        <v>54.89363794915312</v>
+        <v>54.85603812978326</v>
       </c>
     </row>
     <row r="79">
@@ -6262,10 +6262,10 @@
         <v>24.6</v>
       </c>
       <c r="O79" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P79" t="n">
-        <v>36.24764295361059</v>
+        <v>36.58373464659461</v>
       </c>
       <c r="Q79" t="n">
         <v>0.7656499999999937</v>
@@ -6334,10 +6334,10 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P80" t="n">
-        <v>116.5518762551087</v>
+        <v>107.4531011815356</v>
       </c>
       <c r="Q80" t="n">
         <v>-0.3366600000000091</v>
@@ -6346,10 +6346,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S80" t="n">
-        <v>92.94617547281018</v>
+        <v>86.30460829064339</v>
       </c>
       <c r="T80" t="n">
-        <v>92.94617547281018</v>
+        <v>86.30460829064339</v>
       </c>
     </row>
     <row r="81">
@@ -6408,10 +6408,10 @@
         <v>3</v>
       </c>
       <c r="O81" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P81" t="n">
-        <v>110.7914248470779</v>
+        <v>101.7108685415268</v>
       </c>
       <c r="Q81" t="n">
         <v>-0.3366600000000091</v>
@@ -6420,10 +6420,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S81" t="n">
-        <v>88.98250346273767</v>
+        <v>82.34387010564222</v>
       </c>
       <c r="T81" t="n">
-        <v>88.98250346273767</v>
+        <v>82.34387010564222</v>
       </c>
     </row>
     <row r="82">
@@ -6482,10 +6482,10 @@
         <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P82" t="n">
-        <v>106.9511239083908</v>
+        <v>97.8827134481876</v>
       </c>
       <c r="Q82" t="n">
         <v>-3.643590000000017</v>
@@ -6494,10 +6494,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S82" t="n">
-        <v>84.06461123267667</v>
+        <v>77.42240388264057</v>
       </c>
       <c r="T82" t="n">
-        <v>84.06461123267667</v>
+        <v>77.42240388264057</v>
       </c>
     </row>
     <row r="83">
@@ -6556,10 +6556,10 @@
         <v>5.75</v>
       </c>
       <c r="O83" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P83" t="n">
-        <v>105.5110110563831</v>
+        <v>96.4471552881854</v>
       </c>
       <c r="Q83" t="n">
         <v>-0.3366600000000091</v>
@@ -6568,10 +6568,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S83" t="n">
-        <v>85.34913745350454</v>
+        <v>78.71319343605785</v>
       </c>
       <c r="T83" t="n">
-        <v>85.34913745350454</v>
+        <v>78.71319343605785</v>
       </c>
     </row>
     <row r="84">
@@ -6630,10 +6630,10 @@
         <v>6.5</v>
       </c>
       <c r="O84" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P84" t="n">
-        <v>104.0708982043754</v>
+        <v>95.0115971281832</v>
       </c>
       <c r="Q84" t="n">
         <v>-3.643590000000017</v>
@@ -6642,10 +6642,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S84" t="n">
-        <v>82.08277522764041</v>
+        <v>75.44203479013999</v>
       </c>
       <c r="T84" t="n">
-        <v>82.08277522764041</v>
+        <v>75.44203479013999</v>
       </c>
     </row>
     <row r="85">
@@ -6704,10 +6704,10 @@
         <v>9.5</v>
       </c>
       <c r="O85" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P85" t="n">
-        <v>98.31044679634459</v>
+        <v>89.26936448817442</v>
       </c>
       <c r="Q85" t="n">
         <v>-3.643590000000017</v>
@@ -6716,10 +6716,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S85" t="n">
-        <v>78.11910321756793</v>
+        <v>71.48129660513884</v>
       </c>
       <c r="T85" t="n">
-        <v>78.11910321756793</v>
+        <v>71.48129660513884</v>
       </c>
     </row>
     <row r="86">
@@ -6778,10 +6778,10 @@
         <v>10.25</v>
       </c>
       <c r="O86" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P86" t="n">
-        <v>96.87033394433689</v>
+        <v>87.83380632817222</v>
       </c>
       <c r="Q86" t="n">
         <v>-3.643590000000017</v>
@@ -6790,10 +6790,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S86" t="n">
-        <v>77.1281852150498</v>
+        <v>70.49111205888855</v>
       </c>
       <c r="T86" t="n">
-        <v>77.1281852150498</v>
+        <v>70.49111205888855</v>
       </c>
     </row>
     <row r="87">
@@ -6852,10 +6852,10 @@
         <v>11.25</v>
       </c>
       <c r="O87" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P87" t="n">
-        <v>94.9501834749933</v>
+        <v>85.91972878150263</v>
       </c>
       <c r="Q87" t="n">
         <v>-0.3366600000000091</v>
@@ -6864,10 +6864,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S87" t="n">
-        <v>78.08240543503831</v>
+        <v>71.45184009688909</v>
       </c>
       <c r="T87" t="n">
-        <v>78.08240543503831</v>
+        <v>71.45184009688909</v>
       </c>
     </row>
     <row r="88">
@@ -6926,10 +6926,10 @@
         <v>12</v>
       </c>
       <c r="O88" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P88" t="n">
-        <v>93.51007062298561</v>
+        <v>84.48417062150043</v>
       </c>
       <c r="Q88" t="n">
         <v>-0.3366600000000091</v>
@@ -6938,10 +6938,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S88" t="n">
-        <v>77.09148743252018</v>
+        <v>70.4616555506388</v>
       </c>
       <c r="T88" t="n">
-        <v>77.09148743252018</v>
+        <v>70.4616555506388</v>
       </c>
     </row>
     <row r="89">
@@ -7000,10 +7000,10 @@
         <v>12.15</v>
       </c>
       <c r="O89" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001812466671874787</v>
       </c>
       <c r="P89" t="n">
-        <v>93.22204805258406</v>
+        <v>84.19705898949999</v>
       </c>
       <c r="Q89" t="n">
         <v>-0.3366600000000091</v>
@@ -7012,10 +7012,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S89" t="n">
-        <v>76.89330383201656</v>
+        <v>70.26361864138875</v>
       </c>
       <c r="T89" t="n">
-        <v>76.89330383201656</v>
+        <v>70.26361864138875</v>
       </c>
     </row>
     <row r="90">
@@ -7076,10 +7076,10 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P90" t="n">
-        <v>49.81233915569132</v>
+        <v>50.70960006497711</v>
       </c>
       <c r="Q90" t="n">
         <v>1.867959999999982</v>
@@ -7088,10 +7088,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S90" t="n">
-        <v>50.51711791307379</v>
+        <v>50.90225604449002</v>
       </c>
       <c r="T90" t="n">
-        <v>50.51711791307379</v>
+        <v>50.90225604449002</v>
       </c>
     </row>
     <row r="91">
@@ -7150,10 +7150,10 @@
         <v>1.5</v>
       </c>
       <c r="O91" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P91" t="n">
-        <v>45.89969594057135</v>
+        <v>46.8091730298402</v>
       </c>
       <c r="Q91" t="n">
         <v>1.867959999999982</v>
@@ -7162,10 +7162,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S91" t="n">
-        <v>47.82489237402135</v>
+        <v>48.21191393117329</v>
       </c>
       <c r="T91" t="n">
-        <v>47.82489237402135</v>
+        <v>48.21191393117329</v>
       </c>
     </row>
     <row r="92">
@@ -7224,10 +7224,10 @@
         <v>3</v>
       </c>
       <c r="O92" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P92" t="n">
-        <v>41.98705272545138</v>
+        <v>42.90874599470327</v>
       </c>
       <c r="Q92" t="n">
         <v>1.867959999999982</v>
@@ -7236,10 +7236,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S92" t="n">
-        <v>45.1326668349689</v>
+        <v>45.52157181785655</v>
       </c>
       <c r="T92" t="n">
-        <v>45.1326668349689</v>
+        <v>45.52157181785655</v>
       </c>
     </row>
     <row r="93">
@@ -7298,10 +7298,10 @@
         <v>3.15</v>
       </c>
       <c r="O93" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P93" t="n">
-        <v>41.59578840393938</v>
+        <v>42.51870329118958</v>
       </c>
       <c r="Q93" t="n">
         <v>1.867959999999982</v>
@@ -7310,10 +7310,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S93" t="n">
-        <v>44.86344428106366</v>
+        <v>45.25253760652488</v>
       </c>
       <c r="T93" t="n">
-        <v>44.86344428106366</v>
+        <v>45.25253760652488</v>
       </c>
     </row>
     <row r="94">
@@ -7372,10 +7372,10 @@
         <v>4.65</v>
       </c>
       <c r="O94" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P94" t="n">
-        <v>37.6831451888194</v>
+        <v>38.61827625605267</v>
       </c>
       <c r="Q94" t="n">
         <v>1.867959999999982</v>
@@ -7384,10 +7384,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S94" t="n">
-        <v>42.17121874201121</v>
+        <v>42.56219549320814</v>
       </c>
       <c r="T94" t="n">
-        <v>42.17121874201121</v>
+        <v>42.56219549320814</v>
       </c>
     </row>
     <row r="95">
@@ -7446,10 +7446,10 @@
         <v>5.4</v>
       </c>
       <c r="O95" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P95" t="n">
-        <v>35.72682358125942</v>
+        <v>36.6680627384842</v>
       </c>
       <c r="Q95" t="n">
         <v>1.867959999999982</v>
@@ -7458,10 +7458,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S95" t="n">
-        <v>40.82510597248498</v>
+        <v>41.21702443654976</v>
       </c>
       <c r="T95" t="n">
-        <v>40.82510597248498</v>
+        <v>41.21702443654976</v>
       </c>
     </row>
     <row r="96">
@@ -7520,10 +7520,10 @@
         <v>7.15</v>
       </c>
       <c r="O96" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P96" t="n">
-        <v>31.16207316361945</v>
+        <v>32.11756453082447</v>
       </c>
       <c r="Q96" t="n">
         <v>-2.541280000000015</v>
@@ -7532,10 +7532,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S96" t="n">
-        <v>34.65025054579579</v>
+        <v>35.0369931714568</v>
       </c>
       <c r="T96" t="n">
-        <v>34.65025054579579</v>
+        <v>35.0369931714568</v>
       </c>
     </row>
     <row r="97">
@@ -7594,10 +7594,10 @@
         <v>8.4</v>
       </c>
       <c r="O97" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P97" t="n">
-        <v>27.90153715101947</v>
+        <v>28.86720866821037</v>
       </c>
       <c r="Q97" t="n">
         <v>-2.541280000000015</v>
@@ -7606,10 +7606,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S97" t="n">
-        <v>32.40672926325208</v>
+        <v>32.79504141035953</v>
       </c>
       <c r="T97" t="n">
-        <v>32.40672926325208</v>
+        <v>32.79504141035953</v>
       </c>
     </row>
     <row r="98">
@@ -7668,10 +7668,10 @@
         <v>12.4</v>
       </c>
       <c r="O98" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P98" t="n">
-        <v>17.46782191069954</v>
+        <v>18.46606990784525</v>
       </c>
       <c r="Q98" t="n">
         <v>-2.541280000000015</v>
@@ -7680,10 +7680,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S98" t="n">
-        <v>25.22746115911222</v>
+        <v>25.62079577484822</v>
       </c>
       <c r="T98" t="n">
-        <v>25.22746115911222</v>
+        <v>25.62079577484822</v>
       </c>
     </row>
     <row r="99">
@@ -7744,10 +7744,10 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P99" t="n">
-        <v>75.23701399741833</v>
+        <v>76.07106480792947</v>
       </c>
       <c r="Q99" t="n">
         <v>-2.541280000000015</v>
@@ -7756,10 +7756,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S99" t="n">
-        <v>64.97749349154454</v>
+        <v>65.35417427955656</v>
       </c>
       <c r="T99" t="n">
-        <v>64.97749349154454</v>
+        <v>65.35417427955656</v>
       </c>
     </row>
     <row r="100">
@@ -7818,10 +7818,10 @@
         <v>0.25</v>
       </c>
       <c r="O100" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P100" t="n">
-        <v>74.57066677149204</v>
+        <v>75.40679807265761</v>
       </c>
       <c r="Q100" t="n">
         <v>1.867959999999982</v>
@@ -7830,10 +7830,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S100" t="n">
-        <v>67.5529165399216</v>
+        <v>67.93729125535963</v>
       </c>
       <c r="T100" t="n">
-        <v>67.5529165399216</v>
+        <v>67.93729125535963</v>
       </c>
     </row>
     <row r="101">
@@ -7892,10 +7892,10 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P101" t="n">
-        <v>72.57162509371321</v>
+        <v>73.41399786684202</v>
       </c>
       <c r="Q101" t="n">
         <v>-2.541280000000015</v>
@@ -7904,10 +7904,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S101" t="n">
-        <v>63.14348316054073</v>
+        <v>63.52144698454173</v>
       </c>
       <c r="T101" t="n">
-        <v>63.14348316054073</v>
+        <v>63.52144698454173</v>
       </c>
     </row>
     <row r="102">
@@ -7966,10 +7966,10 @@
         <v>2.25</v>
       </c>
       <c r="O102" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P102" t="n">
-        <v>69.2398889640818</v>
+        <v>70.09266419048269</v>
       </c>
       <c r="Q102" t="n">
         <v>1.867959999999982</v>
@@ -7978,10 +7978,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S102" t="n">
-        <v>63.884895877914</v>
+        <v>64.27183666532993</v>
       </c>
       <c r="T102" t="n">
-        <v>63.884895877914</v>
+        <v>64.27183666532993</v>
       </c>
     </row>
     <row r="103">
@@ -8040,10 +8040,10 @@
         <v>3.5</v>
       </c>
       <c r="O103" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P103" t="n">
-        <v>65.90815283445039</v>
+        <v>66.77133051412338</v>
       </c>
       <c r="Q103" t="n">
         <v>-2.541280000000015</v>
@@ -8052,10 +8052,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S103" t="n">
-        <v>58.55845733303124</v>
+        <v>58.93962874700459</v>
       </c>
       <c r="T103" t="n">
-        <v>58.55845733303124</v>
+        <v>58.93962874700459</v>
       </c>
     </row>
     <row r="104">
@@ -8114,10 +8114,10 @@
         <v>4.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P104" t="n">
-        <v>62.576416704819</v>
+        <v>63.44999683776405</v>
       </c>
       <c r="Q104" t="n">
         <v>1.867959999999982</v>
@@ -8126,10 +8126,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S104" t="n">
-        <v>59.29987005040451</v>
+        <v>59.69001842779279</v>
       </c>
       <c r="T104" t="n">
-        <v>59.29987005040451</v>
+        <v>59.69001842779279</v>
       </c>
     </row>
     <row r="105">
@@ -8188,10 +8188,10 @@
         <v>6</v>
       </c>
       <c r="O105" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P105" t="n">
-        <v>59.24468057518759</v>
+        <v>60.12866316140474</v>
       </c>
       <c r="Q105" t="n">
         <v>1.867959999999982</v>
@@ -8200,10 +8200,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S105" t="n">
-        <v>57.00735713664977</v>
+        <v>57.39910930902425</v>
       </c>
       <c r="T105" t="n">
-        <v>57.00735713664977</v>
+        <v>57.39910930902425</v>
       </c>
     </row>
     <row r="106">
@@ -8262,10 +8262,10 @@
         <v>6.15</v>
       </c>
       <c r="O106" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P106" t="n">
-        <v>58.84487223963182</v>
+        <v>59.73010312024162</v>
       </c>
       <c r="Q106" t="n">
         <v>-2.541280000000015</v>
@@ -8274,10 +8274,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S106" t="n">
-        <v>53.69832995587118</v>
+        <v>54.08290141521524</v>
       </c>
       <c r="T106" t="n">
-        <v>53.69832995587118</v>
+        <v>54.08290141521524</v>
       </c>
     </row>
     <row r="107">
@@ -8336,10 +8336,10 @@
         <v>12.65</v>
       </c>
       <c r="O107" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P107" t="n">
-        <v>41.51984436554851</v>
+        <v>42.45916800317315</v>
       </c>
       <c r="Q107" t="n">
         <v>1.867959999999982</v>
@@ -8348,10 +8348,10 @@
         <v>4.95935735305814</v>
       </c>
       <c r="S107" t="n">
-        <v>44.81118843547453</v>
+        <v>45.2114727971755</v>
       </c>
       <c r="T107" t="n">
-        <v>44.81118843547453</v>
+        <v>45.2114727971755</v>
       </c>
     </row>
     <row r="108">
@@ -8410,10 +8410,10 @@
         <v>42.65</v>
       </c>
       <c r="O108" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P108" t="n">
-        <v>-8.235755724571561</v>
+        <v>-7.138155268965818</v>
       </c>
       <c r="Q108" t="n">
         <v>1.867959999999982</v>
@@ -8480,10 +8480,10 @@
         <v>48.65</v>
       </c>
       <c r="O109" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P109" t="n">
-        <v>-16.23192243568694</v>
+        <v>-15.10935609222818</v>
       </c>
       <c r="Q109" t="n">
         <v>1.867959999999982</v>
@@ -8552,10 +8552,10 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P110" t="n">
-        <v>94.84695999337728</v>
+        <v>93.29692233214573</v>
       </c>
       <c r="Q110" t="n">
         <v>-0.3366600000000091</v>
@@ -8564,10 +8564,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>76.57528574592561</v>
+        <v>75.33571313994632</v>
       </c>
       <c r="T110" t="n">
-        <v>76.57528574592561</v>
+        <v>75.33571313994632</v>
       </c>
     </row>
     <row r="111">
@@ -8626,10 +8626,10 @@
         <v>1.25</v>
       </c>
       <c r="O111" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P111" t="n">
-        <v>92.48742877526553</v>
+        <v>90.94485368056885</v>
       </c>
       <c r="Q111" t="n">
         <v>-9.155140000000017</v>
@@ -8638,10 +8638,10 @@
         <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>68.88387980302713</v>
+        <v>67.63076258056846</v>
       </c>
       <c r="T111" t="n">
-        <v>68.88387980302713</v>
+        <v>67.63076258056846</v>
       </c>
     </row>
     <row r="112">
@@ -8700,10 +8700,10 @@
         <v>1.5</v>
       </c>
       <c r="O112" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P112" t="n">
-        <v>92.01552253164317</v>
+        <v>90.47443995025348</v>
       </c>
       <c r="Q112" t="n">
         <v>2.970269999999999</v>
@@ -8712,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>76.90246435250069</v>
+        <v>75.66986368729674</v>
       </c>
       <c r="T112" t="n">
-        <v>76.90246435250069</v>
+        <v>75.66986368729674</v>
       </c>
     </row>
     <row r="113">
@@ -8774,10 +8774,10 @@
         <v>2.25</v>
       </c>
       <c r="O113" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P113" t="n">
-        <v>90.59980380077612</v>
+        <v>89.06319875930737</v>
       </c>
       <c r="Q113" t="n">
         <v>5.174889999999976</v>
@@ -8786,10 +8786,10 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>77.4452943596792</v>
+        <v>76.2171013109165</v>
       </c>
       <c r="T113" t="n">
-        <v>77.4452943596792</v>
+        <v>76.2171013109165</v>
       </c>
     </row>
     <row r="114">
@@ -8848,10 +8848,10 @@
         <v>2.4</v>
       </c>
       <c r="O114" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P114" t="n">
-        <v>90.31666005460271</v>
+        <v>88.78095052111814</v>
       </c>
       <c r="Q114" t="n">
         <v>4.072579999999988</v>
@@ -8860,10 +8860,10 @@
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>76.49198639022009</v>
+        <v>75.26209425579562</v>
       </c>
       <c r="T114" t="n">
-        <v>76.49198639022009</v>
+        <v>75.26209425579562</v>
       </c>
     </row>
     <row r="115">
@@ -8922,10 +8922,10 @@
         <v>2.65</v>
       </c>
       <c r="O115" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P115" t="n">
-        <v>89.84475381098036</v>
+        <v>88.31053679080277</v>
       </c>
       <c r="Q115" t="n">
         <v>-11.35976000000001</v>
@@ -8934,10 +8934,10 @@
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>65.54853574514357</v>
+        <v>64.29307786529405</v>
       </c>
       <c r="T115" t="n">
-        <v>65.54853574514357</v>
+        <v>64.29307786529405</v>
       </c>
     </row>
     <row r="116">
@@ -8996,10 +8996,10 @@
         <v>3.4</v>
       </c>
       <c r="O116" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P116" t="n">
-        <v>88.42903508011331</v>
+        <v>86.89929559985666</v>
       </c>
       <c r="Q116" t="n">
         <v>-2.541280000000015</v>
@@ -9008,10 +9008,10 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>70.6422541990141</v>
+        <v>69.40226368824899</v>
       </c>
       <c r="T116" t="n">
-        <v>70.6422541990141</v>
+        <v>69.40226368824899</v>
       </c>
     </row>
     <row r="117">
@@ -9070,10 +9070,10 @@
         <v>3.5</v>
       </c>
       <c r="O117" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P117" t="n">
-        <v>88.24027258266436</v>
+        <v>86.7111301077305</v>
       </c>
       <c r="Q117" t="n">
         <v>-5.848210000000009</v>
@@ -9082,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>68.23692560121671</v>
+        <v>66.99150135176028</v>
       </c>
       <c r="T117" t="n">
-        <v>68.23692560121671</v>
+        <v>66.99150135176028</v>
       </c>
     </row>
     <row r="118">
@@ -9144,10 +9144,10 @@
         <v>5.5</v>
       </c>
       <c r="O118" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P118" t="n">
-        <v>84.46502263368555</v>
+        <v>82.94782026520753</v>
       </c>
       <c r="Q118" t="n">
         <v>-2.541280000000015</v>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>67.91468233553476</v>
+        <v>66.67671071500494</v>
       </c>
       <c r="T118" t="n">
-        <v>67.91468233553476</v>
+        <v>66.67671071500494</v>
       </c>
     </row>
     <row r="119">
@@ -9218,10 +9218,10 @@
         <v>5.65</v>
       </c>
       <c r="O119" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P119" t="n">
-        <v>84.18187888751214</v>
+        <v>82.6655720270183</v>
       </c>
       <c r="Q119" t="n">
         <v>-0.3366600000000091</v>
@@ -9230,10 +9230,10 @@
         <v>0</v>
       </c>
       <c r="S119" t="n">
-        <v>69.23681858942169</v>
+        <v>68.00267775955162</v>
       </c>
       <c r="T119" t="n">
-        <v>69.23681858942169</v>
+        <v>68.00267775955162</v>
       </c>
     </row>
     <row r="120">
@@ -9292,10 +9292,10 @@
         <v>5.9</v>
       </c>
       <c r="O120" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P120" t="n">
-        <v>83.70997264388978</v>
+        <v>82.19515829670293</v>
       </c>
       <c r="Q120" t="n">
         <v>-1.438970000000012</v>
@@ -9304,10 +9304,10 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>68.15362624551119</v>
+        <v>66.91788246760957</v>
       </c>
       <c r="T120" t="n">
-        <v>68.15362624551119</v>
+        <v>66.91788246760957</v>
       </c>
     </row>
     <row r="121">
@@ -9366,10 +9366,10 @@
         <v>9.9</v>
       </c>
       <c r="O121" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P121" t="n">
-        <v>76.15947274593216</v>
+        <v>74.66853861165696</v>
       </c>
       <c r="Q121" t="n">
         <v>-1.438970000000012</v>
@@ -9378,10 +9378,10 @@
         <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>62.9582512674553</v>
+        <v>61.72635299476374</v>
       </c>
       <c r="T121" t="n">
-        <v>62.9582512674553</v>
+        <v>61.72635299476374</v>
       </c>
     </row>
     <row r="122">
@@ -9440,10 +9440,10 @@
         <v>10.15</v>
       </c>
       <c r="O122" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P122" t="n">
-        <v>75.68756650230982</v>
+        <v>74.19812488134158</v>
       </c>
       <c r="Q122" t="n">
         <v>-2.541280000000015</v>
@@ -9452,10 +9452,10 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>61.87505892354481</v>
+        <v>60.64155770282169</v>
       </c>
       <c r="T122" t="n">
-        <v>61.87505892354481</v>
+        <v>60.64155770282169</v>
       </c>
     </row>
     <row r="123">
@@ -9514,10 +9514,10 @@
         <v>11.65</v>
       </c>
       <c r="O123" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.00220185012159466</v>
       </c>
       <c r="P123" t="n">
-        <v>72.85612904057571</v>
+        <v>71.37564249944934</v>
       </c>
       <c r="Q123" t="n">
         <v>6.277199999999993</v>
@@ -9526,10 +9526,10 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>65.9946445690299</v>
+        <v>64.77733174961806</v>
       </c>
       <c r="T123" t="n">
-        <v>65.9946445690299</v>
+        <v>64.77733174961806</v>
       </c>
     </row>
     <row r="124">
@@ -9590,10 +9590,10 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P124" t="n">
-        <v>123.7900647505644</v>
+        <v>111.0562489713914</v>
       </c>
       <c r="Q124" t="n">
         <v>-1.438970000000012</v>
@@ -9602,10 +9602,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S124" t="n">
-        <v>97.16817269610721</v>
+        <v>87.91792738473602</v>
       </c>
       <c r="T124" t="n">
-        <v>97.16817269610721</v>
+        <v>87.91792738473602</v>
       </c>
     </row>
     <row r="125">
@@ -9664,10 +9664,10 @@
         <v>0.75</v>
       </c>
       <c r="O125" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P125" t="n">
-        <v>122.3418169099271</v>
+        <v>109.612581551554</v>
       </c>
       <c r="Q125" t="n">
         <v>-4.745900000000006</v>
@@ -9676,10 +9676,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S125" t="n">
-        <v>93.89621291816778</v>
+        <v>84.64117532993093</v>
       </c>
       <c r="T125" t="n">
-        <v>93.89621291816778</v>
+        <v>84.64117532993093</v>
       </c>
     </row>
     <row r="126">
@@ -9738,10 +9738,10 @@
         <v>2.5</v>
       </c>
       <c r="O126" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P126" t="n">
-        <v>118.9625719484399</v>
+        <v>106.2440242386003</v>
       </c>
       <c r="Q126" t="n">
         <v>-5.848210000000009</v>
@@ -9750,10 +9750,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S126" t="n">
-        <v>90.8125285496678</v>
+        <v>81.5573687347209</v>
       </c>
       <c r="T126" t="n">
-        <v>90.8125285496678</v>
+        <v>81.5573687347209</v>
       </c>
     </row>
     <row r="127">
@@ -9812,10 +9812,10 @@
         <v>3.25</v>
       </c>
       <c r="O127" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P127" t="n">
-        <v>117.5143241078025</v>
+        <v>104.800356818763</v>
       </c>
       <c r="Q127" t="n">
         <v>0.7656499999999937</v>
@@ -9824,10 +9824,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S127" t="n">
-        <v>94.3669014417664</v>
+        <v>85.12353897891855</v>
       </c>
       <c r="T127" t="n">
-        <v>94.3669014417664</v>
+        <v>85.12353897891855</v>
       </c>
     </row>
     <row r="128">
@@ -9886,10 +9886,10 @@
         <v>3.35</v>
       </c>
       <c r="O128" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P128" t="n">
-        <v>117.3212243957176</v>
+        <v>104.6078678294513</v>
       </c>
       <c r="Q128" t="n">
         <v>7.379509999999982</v>
@@ -9898,10 +9898,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S128" t="n">
-        <v>98.78492114784598</v>
+        <v>89.55271678423539</v>
       </c>
       <c r="T128" t="n">
-        <v>98.78492114784598</v>
+        <v>89.55271678423539</v>
       </c>
     </row>
     <row r="129">
@@ -9960,10 +9960,10 @@
         <v>3.5</v>
       </c>
       <c r="O129" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P129" t="n">
-        <v>117.0315748275901</v>
+        <v>104.3191343454839</v>
       </c>
       <c r="Q129" t="n">
         <v>5.174889999999976</v>
@@ -9972,10 +9972,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S129" t="n">
-        <v>97.06865522136326</v>
+        <v>87.83291179342949</v>
       </c>
       <c r="T129" t="n">
-        <v>97.06865522136326</v>
+        <v>87.83291179342949</v>
       </c>
     </row>
     <row r="130">
@@ -10034,10 +10034,10 @@
         <v>7</v>
       </c>
       <c r="O130" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P130" t="n">
-        <v>110.2730849046158</v>
+        <v>97.58201971957635</v>
       </c>
       <c r="Q130" t="n">
         <v>8.481819999999999</v>
@@ -10046,10 +10046,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S130" t="n">
-        <v>94.69369352327334</v>
+        <v>85.4669221024554</v>
       </c>
       <c r="T130" t="n">
-        <v>94.69369352327334</v>
+        <v>85.4669221024554</v>
       </c>
     </row>
     <row r="131">
@@ -10108,10 +10108,10 @@
         <v>8.25</v>
       </c>
       <c r="O131" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P131" t="n">
-        <v>107.8593385035535</v>
+        <v>95.1759073531808</v>
       </c>
       <c r="Q131" t="n">
         <v>0.7656499999999937</v>
@@ -10120,10 +10120,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S131" t="n">
-        <v>87.72346441114362</v>
+        <v>78.48501927800187</v>
       </c>
       <c r="T131" t="n">
-        <v>87.72346441114362</v>
+        <v>78.48501927800187</v>
       </c>
     </row>
     <row r="132">
@@ -10182,10 +10182,10 @@
         <v>9.5</v>
       </c>
       <c r="O132" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P132" t="n">
-        <v>105.4455921024912</v>
+        <v>92.76979498678527</v>
       </c>
       <c r="Q132" t="n">
         <v>0.7656499999999937</v>
@@ -10194,10 +10194,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S132" t="n">
-        <v>86.06260515348791</v>
+        <v>76.82538935277272</v>
       </c>
       <c r="T132" t="n">
-        <v>86.06260515348791</v>
+        <v>76.82538935277272</v>
       </c>
     </row>
     <row r="133">
@@ -10256,10 +10256,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O133" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P133" t="n">
-        <v>105.3490422464487</v>
+        <v>92.67355049212945</v>
       </c>
       <c r="Q133" t="n">
         <v>-5.848210000000009</v>
@@ -10268,10 +10268,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S133" t="n">
-        <v>81.44528233648967</v>
+        <v>72.19705595642839</v>
       </c>
       <c r="T133" t="n">
-        <v>81.44528233648967</v>
+        <v>72.19705595642839</v>
       </c>
     </row>
     <row r="134">
@@ -10330,10 +10330,10 @@
         <v>10.8</v>
       </c>
       <c r="O134" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P134" t="n">
-        <v>102.9352958453865</v>
+        <v>90.26743812573392</v>
       </c>
       <c r="Q134" t="n">
         <v>-4.745900000000006</v>
@@ -10342,10 +10342,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S134" t="n">
-        <v>80.54290448661598</v>
+        <v>71.29775073108841</v>
       </c>
       <c r="T134" t="n">
-        <v>80.54290448661598</v>
+        <v>71.29775073108841</v>
       </c>
     </row>
     <row r="135">
@@ -10404,10 +10404,10 @@
         <v>16.8</v>
       </c>
       <c r="O135" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P135" t="n">
-        <v>91.3493131202876</v>
+        <v>78.71809876703531</v>
       </c>
       <c r="Q135" t="n">
         <v>-4.745900000000006</v>
@@ -10416,10 +10416,10 @@
         <v>2.087091386303985</v>
       </c>
       <c r="S135" t="n">
-        <v>72.57078004986863</v>
+        <v>63.33152708998841</v>
       </c>
       <c r="T135" t="n">
-        <v>72.57078004986863</v>
+        <v>63.33152708998841</v>
       </c>
     </row>
     <row r="136">
@@ -10478,10 +10478,10 @@
         <v>21.8</v>
       </c>
       <c r="O136" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P136" t="n">
-        <v>83.44710388433776</v>
+        <v>70.83858098185026</v>
       </c>
       <c r="Q136" t="n">
         <v>-1.438970000000012</v>
@@ -10548,10 +10548,10 @@
         <v>23.8</v>
       </c>
       <c r="O137" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P137" t="n">
-        <v>81.51610676348795</v>
+        <v>68.91369108873383</v>
       </c>
       <c r="Q137" t="n">
         <v>4.072579999999988</v>
@@ -10618,10 +10618,10 @@
         <v>24.3</v>
       </c>
       <c r="O138" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001627466671874785</v>
       </c>
       <c r="P138" t="n">
-        <v>81.03335748327549</v>
+        <v>68.43246861545472</v>
       </c>
       <c r="Q138" t="n">
         <v>0.7656499999999937</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P139" t="n">
-        <v>115.1916267960729</v>
+        <v>106.7759732185026</v>
       </c>
       <c r="Q139" t="n">
         <v>6.277199999999993</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>95.12500529944273</v>
+        <v>88.98104284144577</v>
       </c>
       <c r="T139" t="n">
-        <v>95.12500529944273</v>
+        <v>88.98104284144577</v>
       </c>
     </row>
     <row r="140">
@@ -10764,10 +10764,10 @@
         <v>1.75</v>
       </c>
       <c r="O140" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P140" t="n">
-        <v>111.8349306332369</v>
+        <v>103.4298933883771</v>
       </c>
       <c r="Q140" t="n">
         <v>2.970269999999999</v>
@@ -10776,10 +10776,10 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>90.53987357341205</v>
+        <v>84.39209082028114</v>
       </c>
       <c r="T140" t="n">
-        <v>90.53987357341205</v>
+        <v>84.39209082028114</v>
       </c>
     </row>
     <row r="141">
@@ -10838,10 +10838,10 @@
         <v>3.25</v>
       </c>
       <c r="O141" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P141" t="n">
-        <v>108.9577624936631</v>
+        <v>100.5618249625553</v>
       </c>
       <c r="Q141" t="n">
         <v>-5.848210000000009</v>
@@ -10850,10 +10850,10 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>82.49229016599773</v>
+        <v>76.33122643131298</v>
       </c>
       <c r="T141" t="n">
-        <v>82.49229016599773</v>
+        <v>76.33122643131298</v>
       </c>
     </row>
     <row r="142">
@@ -10912,10 +10912,10 @@
         <v>4</v>
       </c>
       <c r="O142" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P142" t="n">
-        <v>107.5191784238762</v>
+        <v>99.12779074964443</v>
       </c>
       <c r="Q142" t="n">
         <v>0.7656499999999937</v>
@@ -10924,10 +10924,10 @@
         <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>86.0533125401106</v>
+        <v>79.90404123572085</v>
       </c>
       <c r="T142" t="n">
-        <v>86.0533125401106</v>
+        <v>79.90404123572085</v>
       </c>
     </row>
     <row r="143">
@@ -10986,10 +10986,10 @@
         <v>4.25</v>
       </c>
       <c r="O143" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P143" t="n">
-        <v>107.0396504006139</v>
+        <v>98.64977934534079</v>
       </c>
       <c r="Q143" t="n">
         <v>-8.052830000000014</v>
@@ -10998,10 +10998,10 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>79.65550592032821</v>
+        <v>73.49173250496486</v>
       </c>
       <c r="T143" t="n">
-        <v>79.65550592032821</v>
+        <v>73.49173250496486</v>
       </c>
     </row>
     <row r="144">
@@ -11060,10 +11060,10 @@
         <v>4.5</v>
       </c>
       <c r="O144" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P144" t="n">
-        <v>106.5601223773516</v>
+        <v>98.17176794103716</v>
       </c>
       <c r="Q144" t="n">
         <v>-11.35976000000001</v>
@@ -11072,10 +11072,10 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>77.05010633945579</v>
+        <v>70.88104727365484</v>
       </c>
       <c r="T144" t="n">
-        <v>77.05010633945579</v>
+        <v>70.88104727365484</v>
       </c>
     </row>
     <row r="145">
@@ -11134,10 +11134,10 @@
         <v>4.75</v>
       </c>
       <c r="O145" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P145" t="n">
-        <v>106.0805943540893</v>
+        <v>97.69375653673353</v>
       </c>
       <c r="Q145" t="n">
         <v>-11.35976000000001</v>
@@ -11146,10 +11146,10 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>76.72015098192941</v>
+        <v>70.55133614201242</v>
       </c>
       <c r="T145" t="n">
-        <v>76.72015098192941</v>
+        <v>70.55133614201242</v>
       </c>
     </row>
     <row r="146">
@@ -11208,10 +11208,10 @@
         <v>5.75</v>
       </c>
       <c r="O146" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P146" t="n">
-        <v>104.1624822610402</v>
+        <v>95.781710919519</v>
       </c>
       <c r="Q146" t="n">
         <v>-5.848210000000009</v>
@@ -11220,10 +11220,10 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>79.19273659073392</v>
+        <v>73.03411511488864</v>
       </c>
       <c r="T146" t="n">
-        <v>79.19273659073392</v>
+        <v>73.03411511488864</v>
       </c>
     </row>
     <row r="147">
@@ -11282,10 +11282,10 @@
         <v>6.5</v>
       </c>
       <c r="O147" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P147" t="n">
-        <v>102.7238981912533</v>
+        <v>94.3476767066081</v>
       </c>
       <c r="Q147" t="n">
         <v>5.174889999999976</v>
@@ -11294,10 +11294,10 @@
         <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>85.78768459597478</v>
+        <v>79.64822871885326</v>
       </c>
       <c r="T147" t="n">
-        <v>85.78768459597478</v>
+        <v>79.64822871885326</v>
       </c>
     </row>
     <row r="148">
@@ -11356,10 +11356,10 @@
         <v>6.65</v>
       </c>
       <c r="O148" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P148" t="n">
-        <v>102.4361813772959</v>
+        <v>94.06086986402592</v>
       </c>
       <c r="Q148" t="n">
         <v>-3.643590000000017</v>
@@ -11368,10 +11368,10 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>79.52186011920293</v>
+        <v>73.36780444075426</v>
       </c>
       <c r="T148" t="n">
-        <v>79.52186011920293</v>
+        <v>73.36780444075426</v>
       </c>
     </row>
     <row r="149">
@@ -11430,10 +11430,10 @@
         <v>7.9</v>
       </c>
       <c r="O149" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P149" t="n">
-        <v>100.0385412609844</v>
+        <v>91.67081284250776</v>
       </c>
       <c r="Q149" t="n">
         <v>6.277199999999993</v>
@@ -11442,10 +11442,10 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>84.69841600160908</v>
+        <v>78.56217108154485</v>
       </c>
       <c r="T149" t="n">
-        <v>84.69841600160908</v>
+        <v>78.56217108154485</v>
       </c>
     </row>
     <row r="150">
@@ -11504,10 +11504,10 @@
         <v>9.15</v>
       </c>
       <c r="O150" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P150" t="n">
-        <v>97.64090114467297</v>
+        <v>89.28075582098958</v>
       </c>
       <c r="Q150" t="n">
         <v>4.072579999999988</v>
@@ -11516,10 +11516,10 @@
         <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>81.53167639841317</v>
+        <v>75.39296602355427</v>
       </c>
       <c r="T150" t="n">
-        <v>81.53167639841317</v>
+        <v>75.39296602355427</v>
       </c>
     </row>
     <row r="151">
@@ -11578,10 +11578,10 @@
         <v>11.65</v>
       </c>
       <c r="O151" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P151" t="n">
-        <v>92.84562091205002</v>
+        <v>84.50064177795326</v>
       </c>
       <c r="Q151" t="n">
         <v>6.277199999999993</v>
@@ -11590,10 +11590,10 @@
         <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>79.74908563871335</v>
+        <v>73.61650410690832</v>
       </c>
       <c r="T151" t="n">
-        <v>79.74908563871335</v>
+        <v>73.61650410690832</v>
       </c>
     </row>
     <row r="152">
@@ -11652,10 +11652,10 @@
         <v>19.65</v>
       </c>
       <c r="O152" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P152" t="n">
-        <v>77.50072416765663</v>
+        <v>69.204276840237</v>
       </c>
       <c r="Q152" t="n">
         <v>2.970269999999999</v>
@@ -11664,10 +11664,10 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>66.91506997452312</v>
+        <v>60.78477379468286</v>
       </c>
       <c r="T152" t="n">
-        <v>66.91506997452312</v>
+        <v>60.78477379468286</v>
       </c>
     </row>
     <row r="153">
@@ -11726,10 +11726,10 @@
         <v>22.65</v>
       </c>
       <c r="O153" t="n">
-        <v>0.001926331139196653</v>
+        <v>0.001847466671874784</v>
       </c>
       <c r="P153" t="n">
-        <v>74.3026660880125</v>
+        <v>66.01573019361429</v>
       </c>
       <c r="Q153" t="n">
         <v>-0.3366600000000091</v>
@@ -11798,10 +11798,10 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P154" t="n">
-        <v>79.17473609131166</v>
+        <v>79.23493723555666</v>
       </c>
       <c r="Q154" t="n">
         <v>-0.3366600000000091</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>70.14173331265708</v>
+        <v>70.23521717473741</v>
       </c>
       <c r="T154" t="n">
-        <v>70.14173331265708</v>
+        <v>70.23521717473741</v>
       </c>
     </row>
     <row r="155">
@@ -11872,10 +11872,10 @@
         <v>0.1</v>
       </c>
       <c r="O155" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P155" t="n">
-        <v>78.80949540799779</v>
+        <v>78.8706676620981</v>
       </c>
       <c r="Q155" t="n">
         <v>-0.3366600000000091</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>69.89041719681022</v>
+        <v>69.98396012897112</v>
       </c>
       <c r="T155" t="n">
-        <v>69.89041719681022</v>
+        <v>69.98396012897112</v>
       </c>
     </row>
     <row r="156">
@@ -11946,10 +11946,10 @@
         <v>3.1</v>
       </c>
       <c r="O156" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P156" t="n">
-        <v>67.85227490858145</v>
+        <v>67.94258045834127</v>
       </c>
       <c r="Q156" t="n">
         <v>-9.155140000000017</v>
@@ -11958,10 +11958,10 @@
         <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>56.28308245914786</v>
+        <v>56.36365115686871</v>
       </c>
       <c r="T156" t="n">
-        <v>56.28308245914786</v>
+        <v>56.36365115686871</v>
       </c>
     </row>
     <row r="157">
@@ -12020,10 +12020,10 @@
         <v>4.6</v>
       </c>
       <c r="O157" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P157" t="n">
-        <v>62.3736646588733</v>
+        <v>62.47853685646285</v>
       </c>
       <c r="Q157" t="n">
         <v>-4.745900000000006</v>
@@ -12032,10 +12032,10 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>55.54726635257273</v>
+        <v>55.63609426993105</v>
       </c>
       <c r="T157" t="n">
-        <v>55.54726635257273</v>
+        <v>55.63609426993105</v>
       </c>
     </row>
     <row r="158">
@@ -12094,10 +12094,10 @@
         <v>4.63</v>
       </c>
       <c r="O158" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P158" t="n">
-        <v>62.26409245387913</v>
+        <v>62.36925598442528</v>
       </c>
       <c r="Q158" t="n">
         <v>-0.3366600000000091</v>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>58.50579714894668</v>
+        <v>58.60201595575793</v>
       </c>
       <c r="T158" t="n">
-        <v>58.50579714894668</v>
+        <v>58.60201595575793</v>
       </c>
     </row>
     <row r="159">
@@ -12168,10 +12168,10 @@
         <v>8.629999999999999</v>
       </c>
       <c r="O159" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P159" t="n">
-        <v>47.65446512132404</v>
+        <v>47.79847304608283</v>
       </c>
       <c r="Q159" t="n">
         <v>-0.3366600000000091</v>
@@ -12180,10 +12180,10 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>48.45315251507161</v>
+        <v>48.55173412510612</v>
       </c>
       <c r="T159" t="n">
-        <v>48.45315251507161</v>
+        <v>48.55173412510612</v>
       </c>
     </row>
     <row r="160">
@@ -12242,10 +12242,10 @@
         <v>24.63</v>
       </c>
       <c r="O160" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P160" t="n">
-        <v>-2.328629712163917</v>
+        <v>-2.050282398957506</v>
       </c>
       <c r="Q160" t="n">
         <v>-9.155140000000017</v>
@@ -12314,10 +12314,10 @@
         <v>0</v>
       </c>
       <c r="O161" t="n">
-        <v>0.0001988387815159469</v>
+        <v>-0.000249324191168027</v>
       </c>
       <c r="P161" t="n">
-        <v>134.4719584954236</v>
+        <v>115.7512569717106</v>
       </c>
       <c r="Q161" t="n">
         <v>-4.745900000000006</v>
@@ -12326,10 +12326,10 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>102.9656144347339</v>
+        <v>89.30625583209344</v>
       </c>
       <c r="T161" t="n">
-        <v>102.9656144347339</v>
+        <v>89.30625583209344</v>
       </c>
     </row>
     <row r="162">
@@ -12388,10 +12388,10 @@
         <v>2.5</v>
       </c>
       <c r="O162" t="n">
-        <v>0.0001988387815159469</v>
+        <v>-0.000249324191168027</v>
       </c>
       <c r="P162" t="n">
-        <v>123.8874699707664</v>
+        <v>105.200070769316</v>
       </c>
       <c r="Q162" t="n">
         <v>-2.541280000000015</v>
@@ -12400,10 +12400,10 @@
         <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>97.19956452535256</v>
+        <v>83.54916350512464</v>
       </c>
       <c r="T162" t="n">
-        <v>97.19956452535256</v>
+        <v>83.54916350512464</v>
       </c>
     </row>
     <row r="163">
@@ -12462,10 +12462,10 @@
         <v>3.25</v>
       </c>
       <c r="O163" t="n">
-        <v>0.0001988387815159469</v>
+        <v>-0.000249324191168027</v>
       </c>
       <c r="P163" t="n">
-        <v>120.7121234133692</v>
+        <v>102.0347149085976</v>
       </c>
       <c r="Q163" t="n">
         <v>6.277199999999993</v>
@@ -12474,10 +12474,10 @@
         <v>0</v>
       </c>
       <c r="S163" t="n">
-        <v>101.082511970125</v>
+        <v>87.44843858621404</v>
       </c>
       <c r="T163" t="n">
-        <v>101.082511970125</v>
+        <v>87.44843858621404</v>
       </c>
     </row>
     <row r="164">
@@ -12536,10 +12536,10 @@
         <v>4.25</v>
       </c>
       <c r="O164" t="n">
-        <v>0.0001988387815159469</v>
+        <v>-0.000249324191168027</v>
       </c>
       <c r="P164" t="n">
-        <v>116.4783280035063</v>
+        <v>97.81424042763977</v>
       </c>
       <c r="Q164" t="n">
         <v>1.867959999999982</v>
@@ -12548,10 +12548,10 @@
         <v>0</v>
       </c>
       <c r="S164" t="n">
-        <v>95.13538124901886</v>
+        <v>81.4960430959584</v>
       </c>
       <c r="T164" t="n">
-        <v>95.13538124901886</v>
+        <v>81.4960430959584</v>
       </c>
     </row>
     <row r="165">
@@ -12610,10 +12610,10 @@
         <v>7.25</v>
       </c>
       <c r="O165" t="n">
-        <v>0.0001988387815159469</v>
+        <v>-0.000249324191168027</v>
       </c>
       <c r="P165" t="n">
-        <v>103.7769417739177</v>
+        <v>85.15281698476623</v>
       </c>
       <c r="Q165" t="n">
         <v>-8.052830000000014</v>
@@ -12622,10 +12622,10 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>79.56943330904649</v>
+        <v>65.91983072485904</v>
       </c>
       <c r="T165" t="n">
-        <v>79.56943330904649</v>
+        <v>65.91983072485904</v>
       </c>
     </row>
     <row r="166">
@@ -12684,10 +12684,10 @@
         <v>8.25</v>
       </c>
       <c r="O166" t="n">
-        <v>0.0001988387815159469</v>
+        <v>-0.000249324191168027</v>
       </c>
       <c r="P166" t="n">
-        <v>99.54314636405485</v>
+        <v>80.93234250380839</v>
       </c>
       <c r="Q166" t="n">
         <v>-13.56438000000001</v>
@@ -12696,10 +12696,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>72.86382118015835</v>
+        <v>59.2071105347142</v>
       </c>
       <c r="T166" t="n">
-        <v>72.86382118015835</v>
+        <v>59.2071105347142</v>
       </c>
     </row>
     <row r="167">
@@ -12760,10 +12760,10 @@
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P167" t="n">
-        <v>113.4891925136961</v>
+        <v>106.7291426028191</v>
       </c>
       <c r="Q167" t="n">
         <v>-2.541280000000015</v>
@@ -12772,10 +12772,10 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>92.2359844156136</v>
+        <v>87.49782722441054</v>
       </c>
       <c r="T167" t="n">
-        <v>92.2359844156136</v>
+        <v>87.49782722441054</v>
       </c>
     </row>
     <row r="168">
@@ -12834,10 +12834,10 @@
         <v>2.5</v>
       </c>
       <c r="O168" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P168" t="n">
-        <v>104.1170325688004</v>
+        <v>97.38190156018119</v>
       </c>
       <c r="Q168" t="n">
         <v>1.867959999999982</v>
@@ -12846,10 +12846,10 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>88.82108070747897</v>
+        <v>84.09181243655942</v>
       </c>
       <c r="T168" t="n">
-        <v>88.82108070747897</v>
+        <v>84.09181243655942</v>
       </c>
     </row>
     <row r="169">
@@ -12908,10 +12908,10 @@
         <v>2.6</v>
       </c>
       <c r="O169" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P169" t="n">
-        <v>103.7421461710046</v>
+        <v>97.00801191847567</v>
       </c>
       <c r="Q169" t="n">
         <v>6.277199999999993</v>
@@ -12920,10 +12920,10 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>91.59705316503651</v>
+        <v>86.87521869261991</v>
       </c>
       <c r="T169" t="n">
-        <v>91.59705316503651</v>
+        <v>86.87521869261991</v>
       </c>
     </row>
     <row r="170">
@@ -12982,10 +12982,10 @@
         <v>4.1</v>
       </c>
       <c r="O170" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P170" t="n">
-        <v>98.11885020406714</v>
+        <v>91.39966729289296</v>
       </c>
       <c r="Q170" t="n">
         <v>-15.76900000000001</v>
@@ -12994,10 +12994,10 @@
         <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>72.55812740583885</v>
+        <v>67.80033654239131</v>
       </c>
       <c r="T170" t="n">
-        <v>72.55812740583885</v>
+        <v>67.80033654239131</v>
       </c>
     </row>
     <row r="171">
@@ -13056,10 +13056,10 @@
         <v>6.6</v>
       </c>
       <c r="O171" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P171" t="n">
-        <v>88.74669025917143</v>
+        <v>82.0524262502551</v>
       </c>
       <c r="Q171" t="n">
         <v>1.867959999999982</v>
@@ -13068,10 +13068,10 @@
         <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>78.24500059108824</v>
+        <v>73.51821815321051</v>
       </c>
       <c r="T171" t="n">
-        <v>78.24500059108824</v>
+        <v>73.51821815321051</v>
       </c>
     </row>
     <row r="172">
@@ -13130,10 +13130,10 @@
         <v>8.1</v>
       </c>
       <c r="O172" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P172" t="n">
-        <v>83.12339429223401</v>
+        <v>76.44408162467238</v>
       </c>
       <c r="Q172" t="n">
         <v>-4.745900000000006</v>
@@ -13142,10 +13142,10 @@
         <v>0</v>
       </c>
       <c r="S172" t="n">
-        <v>69.82481454083866</v>
+        <v>65.08788180143063</v>
       </c>
       <c r="T172" t="n">
-        <v>69.82481454083866</v>
+        <v>65.08788180143063</v>
       </c>
     </row>
     <row r="173">
@@ -13204,10 +13204,10 @@
         <v>9.6</v>
       </c>
       <c r="O173" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P173" t="n">
-        <v>77.50009832529658</v>
+        <v>70.83573699908966</v>
       </c>
       <c r="Q173" t="n">
         <v>-13.56438000000001</v>
@@ -13216,10 +13216,10 @@
         <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>59.88766567502502</v>
+        <v>55.13689604987233</v>
       </c>
       <c r="T173" t="n">
-        <v>59.88766567502502</v>
+        <v>55.13689604987233</v>
       </c>
     </row>
     <row r="174">
@@ -13278,10 +13278,10 @@
         <v>10.35</v>
       </c>
       <c r="O174" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P174" t="n">
-        <v>74.68845034182786</v>
+        <v>68.03156468629831</v>
       </c>
       <c r="Q174" t="n">
         <v>-6.950520000000012</v>
@@ -13290,10 +13290,10 @@
         <v>0</v>
       </c>
       <c r="S174" t="n">
-        <v>62.50390531993825</v>
+        <v>57.76465017298514</v>
       </c>
       <c r="T174" t="n">
-        <v>62.50390531993825</v>
+        <v>57.76465017298514</v>
       </c>
     </row>
     <row r="175">
@@ -13352,10 +13352,10 @@
         <v>10.85</v>
       </c>
       <c r="O175" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P175" t="n">
-        <v>72.81401835284873</v>
+        <v>66.16211647777072</v>
       </c>
       <c r="Q175" t="n">
         <v>-4.745900000000006</v>
@@ -13364,10 +13364,10 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>62.73110226764974</v>
+        <v>57.99583685528194</v>
       </c>
       <c r="T175" t="n">
-        <v>62.73110226764974</v>
+        <v>57.99583685528194</v>
       </c>
     </row>
     <row r="176">
@@ -13426,10 +13426,10 @@
         <v>13.35</v>
       </c>
       <c r="O176" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001945665128151592</v>
       </c>
       <c r="P176" t="n">
-        <v>63.44185840795301</v>
+        <v>56.81487543513287</v>
       </c>
       <c r="Q176" t="n">
         <v>-15.76900000000001</v>
@@ -13438,10 +13438,10 @@
         <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>48.69745885056705</v>
+        <v>43.94527626898213</v>
       </c>
       <c r="T176" t="n">
-        <v>48.69745885056705</v>
+        <v>43.94527626898213</v>
       </c>
     </row>
     <row r="177">
@@ -13502,10 +13502,10 @@
         <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P177" t="n">
-        <v>110.5169281818924</v>
+        <v>105.0573494605652</v>
       </c>
       <c r="Q177" t="n">
         <v>-2.541280000000015</v>
@@ -13514,10 +13514,10 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>90.19081814234501</v>
+        <v>86.38983868022234</v>
       </c>
       <c r="T177" t="n">
-        <v>90.19081814234501</v>
+        <v>86.38983868022234</v>
       </c>
     </row>
     <row r="178">
@@ -13576,10 +13576,10 @@
         <v>7</v>
       </c>
       <c r="O178" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P178" t="n">
-        <v>87.9858348302626</v>
+        <v>82.59660341035433</v>
       </c>
       <c r="Q178" t="n">
         <v>-2.541280000000015</v>
@@ -13588,10 +13588,10 @@
         <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>74.68754283484357</v>
+        <v>70.89740914595885</v>
       </c>
       <c r="T178" t="n">
-        <v>74.68754283484357</v>
+        <v>70.89740914595885</v>
       </c>
     </row>
     <row r="179">
@@ -13650,10 +13650,10 @@
         <v>8.5</v>
       </c>
       <c r="O179" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P179" t="n">
-        <v>83.1577433977705</v>
+        <v>77.78358639959484</v>
       </c>
       <c r="Q179" t="n">
         <v>-6.950520000000012</v>
@@ -13662,10 +13662,10 @@
         <v>0</v>
       </c>
       <c r="S179" t="n">
-        <v>68.33148678067953</v>
+        <v>64.53630401763131</v>
       </c>
       <c r="T179" t="n">
-        <v>68.33148678067953</v>
+        <v>64.53630401763131</v>
       </c>
     </row>
     <row r="180">
@@ -13724,10 +13724,10 @@
         <v>10</v>
       </c>
       <c r="O180" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P180" t="n">
-        <v>78.3296519652784</v>
+        <v>72.97056938883537</v>
       </c>
       <c r="Q180" t="n">
         <v>-11.35976000000001</v>
@@ -13736,10 +13736,10 @@
         <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>61.97543072651549</v>
+        <v>58.1751988893038</v>
       </c>
       <c r="T180" t="n">
-        <v>61.97543072651549</v>
+        <v>58.1751988893038</v>
       </c>
     </row>
     <row r="181">
@@ -13798,10 +13798,10 @@
         <v>10.15</v>
       </c>
       <c r="O181" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P181" t="n">
-        <v>77.8468428220292</v>
+        <v>72.48926768775942</v>
       </c>
       <c r="Q181" t="n">
         <v>-2.541280000000015</v>
@@ -13810,10 +13810,10 @@
         <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>67.71106894646793</v>
+        <v>63.92581585554026</v>
       </c>
       <c r="T181" t="n">
-        <v>67.71106894646793</v>
+        <v>63.92581585554026</v>
       </c>
     </row>
     <row r="182">
@@ -13872,10 +13872,10 @@
         <v>12.15</v>
       </c>
       <c r="O182" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P182" t="n">
-        <v>71.4093875787064</v>
+        <v>66.07191167341344</v>
       </c>
       <c r="Q182" t="n">
         <v>-11.35976000000001</v>
@@ -13884,10 +13884,10 @@
         <v>0</v>
       </c>
       <c r="S182" t="n">
-        <v>57.2137104534972</v>
+        <v>53.41680981806572</v>
       </c>
       <c r="T182" t="n">
-        <v>57.2137104534972</v>
+        <v>53.41680981806572</v>
       </c>
     </row>
     <row r="183">
@@ -13946,10 +13946,10 @@
         <v>17.15</v>
       </c>
       <c r="O183" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P183" t="n">
-        <v>55.3157494703994</v>
+        <v>50.0285216375485</v>
       </c>
       <c r="Q183" t="n">
         <v>-2.541280000000015</v>
@@ -13958,10 +13958,10 @@
         <v>0</v>
       </c>
       <c r="S183" t="n">
-        <v>52.20779363896648</v>
+        <v>48.43338632127676</v>
       </c>
       <c r="T183" t="n">
-        <v>52.20779363896648</v>
+        <v>48.43338632127676</v>
       </c>
     </row>
     <row r="184">
@@ -14020,10 +14020,10 @@
         <v>30.15</v>
       </c>
       <c r="O184" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P184" t="n">
-        <v>29.80741474235357</v>
+        <v>24.59821122687964</v>
       </c>
       <c r="Q184" t="n">
         <v>-2.541280000000015</v>
@@ -14090,10 +14090,10 @@
         <v>30.65</v>
       </c>
       <c r="O185" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>-0.0001197692491645485</v>
       </c>
       <c r="P185" t="n">
-        <v>29.00273283693822</v>
+        <v>23.7960417250864</v>
       </c>
       <c r="Q185" t="n">
         <v>-2.541280000000015</v>
@@ -14162,10 +14162,10 @@
         <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P186" t="n">
-        <v>98.14206106306467</v>
+        <v>97.78186400271694</v>
       </c>
       <c r="Q186" t="n">
         <v>-2.541280000000015</v>
@@ -14174,10 +14174,10 @@
         <v>0</v>
       </c>
       <c r="S186" t="n">
-        <v>81.67587531010754</v>
+        <v>81.50741781542675</v>
       </c>
       <c r="T186" t="n">
-        <v>81.67587531010754</v>
+        <v>81.50741781542675</v>
       </c>
     </row>
     <row r="187">
@@ -14236,10 +14236,10 @@
         <v>1.5</v>
       </c>
       <c r="O187" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P187" t="n">
-        <v>93.35834335226056</v>
+        <v>93.01308216859013</v>
       </c>
       <c r="Q187" t="n">
         <v>-2.541280000000015</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>78.38427771621618</v>
+        <v>78.21812295565999</v>
       </c>
       <c r="T187" t="n">
-        <v>78.38427771621618</v>
+        <v>78.21812295565999</v>
       </c>
     </row>
     <row r="188">
@@ -14310,10 +14310,10 @@
         <v>6.5</v>
       </c>
       <c r="O188" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P188" t="n">
-        <v>77.41261764958016</v>
+        <v>77.11714272150073</v>
       </c>
       <c r="Q188" t="n">
         <v>-2.541280000000015</v>
@@ -14322,10 +14322,10 @@
         <v>0</v>
       </c>
       <c r="S188" t="n">
-        <v>67.41228573657821</v>
+        <v>67.25380675643741</v>
       </c>
       <c r="T188" t="n">
-        <v>67.41228573657821</v>
+        <v>67.25380675643741</v>
       </c>
     </row>
     <row r="189">
@@ -14384,10 +14384,10 @@
         <v>8</v>
       </c>
       <c r="O189" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P189" t="n">
-        <v>72.62889993877604</v>
+        <v>72.34836088737391</v>
       </c>
       <c r="Q189" t="n">
         <v>-2.541280000000015</v>
@@ -14396,10 +14396,10 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>64.12068814268683</v>
+        <v>63.96451189667064</v>
       </c>
       <c r="T189" t="n">
-        <v>64.12068814268683</v>
+        <v>63.96451189667064</v>
       </c>
     </row>
     <row r="190">
@@ -14458,10 +14458,10 @@
         <v>10</v>
       </c>
       <c r="O190" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P190" t="n">
-        <v>66.25060965770388</v>
+        <v>65.98998510853816</v>
       </c>
       <c r="Q190" t="n">
         <v>-2.541280000000015</v>
@@ -14470,10 +14470,10 @@
         <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>59.73189135083164</v>
+        <v>59.57878541698162</v>
       </c>
       <c r="T190" t="n">
-        <v>59.73189135083164</v>
+        <v>59.57878541698162</v>
       </c>
     </row>
     <row r="191">
@@ -14532,10 +14532,10 @@
         <v>10.5</v>
       </c>
       <c r="O191" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P191" t="n">
-        <v>64.65603708743583</v>
+        <v>64.40039116382923</v>
       </c>
       <c r="Q191" t="n">
         <v>-11.35976000000001</v>
@@ -14544,10 +14544,10 @@
         <v>0</v>
       </c>
       <c r="S191" t="n">
-        <v>52.56684089061181</v>
+        <v>52.39975619794582</v>
       </c>
       <c r="T191" t="n">
-        <v>52.56684089061181</v>
+        <v>52.39975619794582</v>
       </c>
     </row>
     <row r="192">
@@ -14608,10 +14608,10 @@
         <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P192" t="n">
-        <v>99.25158543141933</v>
+        <v>99.25848045162196</v>
       </c>
       <c r="Q192" t="n">
         <v>-0.3366600000000091</v>
@@ -14620,10 +14620,10 @@
         <v>0</v>
       </c>
       <c r="S192" t="n">
-        <v>83.95628362183696</v>
+        <v>84.04657195376794</v>
       </c>
       <c r="T192" t="n">
-        <v>83.95628362183696</v>
+        <v>84.04657195376794</v>
       </c>
     </row>
     <row r="193">
@@ -14682,10 +14682,10 @@
         <v>5</v>
       </c>
       <c r="O193" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P193" t="n">
-        <v>80.70737346572176</v>
+        <v>80.76357423914874</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.3366600000000091</v>
@@ -14694,10 +14694,10 @@
         <v>0</v>
       </c>
       <c r="S193" t="n">
-        <v>71.19631591951168</v>
+        <v>71.28960339185934</v>
       </c>
       <c r="T193" t="n">
-        <v>71.19631591951168</v>
+        <v>71.28960339185934</v>
       </c>
     </row>
     <row r="194">
@@ -14756,10 +14756,10 @@
         <v>8.5</v>
       </c>
       <c r="O194" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P194" t="n">
-        <v>67.72642508973345</v>
+        <v>67.81713989041747</v>
       </c>
       <c r="Q194" t="n">
         <v>-9.155140000000017</v>
@@ -14768,10 +14768,10 @@
         <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>56.19648726562794</v>
+        <v>56.27712779940973</v>
       </c>
       <c r="T194" t="n">
-        <v>56.19648726562794</v>
+        <v>56.27712779940973</v>
       </c>
     </row>
     <row r="195">
@@ -14830,10 +14830,10 @@
         <v>10</v>
       </c>
       <c r="O195" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P195" t="n">
-        <v>62.16316150002419</v>
+        <v>62.2686680266755</v>
       </c>
       <c r="Q195" t="n">
         <v>-6.950520000000012</v>
@@ -14842,10 +14842,10 @@
         <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>53.88545977049438</v>
+        <v>53.97068663061555</v>
       </c>
       <c r="T195" t="n">
-        <v>53.88545977049438</v>
+        <v>53.97068663061555</v>
       </c>
     </row>
     <row r="196">
@@ -14904,10 +14904,10 @@
         <v>10.5</v>
       </c>
       <c r="O196" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P196" t="n">
-        <v>60.30874030345443</v>
+        <v>60.41917740542817</v>
       </c>
       <c r="Q196" t="n">
         <v>-0.3366600000000091</v>
@@ -14916,10 +14916,10 @@
         <v>0</v>
       </c>
       <c r="S196" t="n">
-        <v>57.16035144695387</v>
+        <v>57.25693797375984</v>
       </c>
       <c r="T196" t="n">
-        <v>57.16035144695387</v>
+        <v>57.25693797375984</v>
       </c>
     </row>
     <row r="197">
@@ -14978,10 +14978,10 @@
         <v>12</v>
       </c>
       <c r="O197" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P197" t="n">
-        <v>54.74547671374516</v>
+        <v>54.87070554168621</v>
       </c>
       <c r="Q197" t="n">
         <v>-0.3366600000000091</v>
@@ -14990,10 +14990,10 @@
         <v>0</v>
       </c>
       <c r="S197" t="n">
-        <v>53.33236113625629</v>
+        <v>53.42984740518726</v>
       </c>
       <c r="T197" t="n">
-        <v>53.33236113625629</v>
+        <v>53.42984740518726</v>
       </c>
     </row>
     <row r="198">
@@ -15052,10 +15052,10 @@
         <v>12</v>
       </c>
       <c r="O198" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P198" t="n">
-        <v>54.74547671374516</v>
+        <v>54.87070554168621</v>
       </c>
       <c r="Q198" t="n">
         <v>-0.3366600000000091</v>
@@ -15064,10 +15064,10 @@
         <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>53.33236113625629</v>
+        <v>53.42984740518726</v>
       </c>
       <c r="T198" t="n">
-        <v>53.33236113625629</v>
+        <v>53.42984740518726</v>
       </c>
     </row>
     <row r="199">
@@ -15126,10 +15126,10 @@
         <v>14.5</v>
       </c>
       <c r="O199" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P199" t="n">
-        <v>45.47337073089637</v>
+        <v>45.62325243544959</v>
       </c>
       <c r="Q199" t="n">
         <v>-9.155140000000017</v>
@@ -15138,10 +15138,10 @@
         <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>40.88452602283762</v>
+        <v>40.96876552511939</v>
       </c>
       <c r="T199" t="n">
-        <v>40.88452602283762</v>
+        <v>40.96876552511939</v>
       </c>
     </row>
     <row r="200">
@@ -15200,10 +15200,10 @@
         <v>18.5</v>
       </c>
       <c r="O200" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P200" t="n">
-        <v>30.63800115833831</v>
+        <v>30.827327465471</v>
       </c>
       <c r="Q200" t="n">
         <v>-0.3366600000000091</v>
@@ -15212,10 +15212,10 @@
         <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>36.74440312323343</v>
+        <v>36.84578827470605</v>
       </c>
       <c r="T200" t="n">
-        <v>36.74440312323343</v>
+        <v>36.84578827470605</v>
       </c>
     </row>
     <row r="201">
@@ -15274,10 +15274,10 @@
         <v>18.6</v>
       </c>
       <c r="O201" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P201" t="n">
-        <v>30.26711691902436</v>
+        <v>30.45742934122154</v>
       </c>
       <c r="Q201" t="n">
         <v>-9.155140000000017</v>
@@ -15286,10 +15286,10 @@
         <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>30.42135250693089</v>
+        <v>30.50805130435434</v>
       </c>
       <c r="T201" t="n">
-        <v>30.42135250693089</v>
+        <v>30.50805130435434</v>
       </c>
     </row>
     <row r="202">
@@ -15348,10 +15348,10 @@
         <v>28.6</v>
       </c>
       <c r="O202" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P202" t="n">
-        <v>9.126809388169704</v>
+        <v>9.374795670534468</v>
       </c>
       <c r="Q202" t="n">
         <v>-0.3366600000000091</v>
@@ -15418,10 +15418,10 @@
         <v>37.6</v>
       </c>
       <c r="O203" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P203" t="n">
-        <v>-7.562981380958121</v>
+        <v>-7.270619920691445</v>
       </c>
       <c r="Q203" t="n">
         <v>-0.3366600000000091</v>
@@ -15488,10 +15488,10 @@
         <v>43.1</v>
       </c>
       <c r="O204" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P204" t="n">
-        <v>-17.76229796209178</v>
+        <v>-17.44281833755171</v>
       </c>
       <c r="Q204" t="n">
         <v>-0.3366600000000091</v>
@@ -15558,10 +15558,10 @@
         <v>57.1</v>
       </c>
       <c r="O205" t="n">
-        <v>6.343626299336333e-06</v>
+        <v>0.000105394663434769</v>
       </c>
       <c r="P205" t="n">
-        <v>-43.72419471406835</v>
+        <v>-43.33568703501423</v>
       </c>
       <c r="Q205" t="n">
         <v>-9.155140000000017</v>
